--- a/Таблица для оценки ЖК.xlsx
+++ b/Таблица для оценки ЖК.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katya_pozd/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F98DCC-562E-D34D-A7FE-EDA5B85FD845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C863C56F-EB28-BC41-BB9E-FA7C6100F550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="760" windowWidth="38080" windowHeight="18980" firstSheet="1" activeTab="3" xr2:uid="{CD488BF6-AAE2-A54B-8C2E-0F83BB345587}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="161">
   <si>
     <t>1.1.</t>
   </si>
@@ -1601,7 +1601,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1652,27 +1652,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1838,8 +1822,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1860,19 +1867,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD4C9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD38F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1894,6 +1889,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="64">
     <border>
@@ -2659,9 +2660,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2681,7 +2682,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2692,26 +2693,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2724,32 +2720,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2769,46 +2765,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="8" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2818,211 +2814,107 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="15" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="20" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="9" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="20" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="21" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="24" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="9" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3031,116 +2923,182 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="53" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="53" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="58" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="59" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="56" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="59" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3151,12 +3109,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill>
@@ -3165,9 +3160,38 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FFB56CFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB56CFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB56CFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3179,16 +3203,21 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FFB56CFF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FFB56CFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3219,6 +3248,18 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB56CFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
@@ -3234,10 +3275,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFF8CB"/>
       <color rgb="FFF4FFC0"/>
       <color rgb="FFFFF5FF"/>
       <color rgb="FFB56CFF"/>
-      <color rgb="FFFFF8CB"/>
       <color rgb="FFFFD38F"/>
       <color rgb="FFFFD4C9"/>
       <color rgb="FFE1F1FF"/>
@@ -3607,8 +3648,8 @@
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
     <col min="2" max="2" width="8.1640625" customWidth="1"/>
-    <col min="3" max="3" width="29" style="31" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="31" customWidth="1"/>
+    <col min="3" max="3" width="29" style="26" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="26" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
     <col min="6" max="6" width="22.1640625" customWidth="1"/>
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
@@ -3621,58 +3662,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="134" t="s">
+      <c r="B1" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="115" t="s">
+      <c r="C1" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="38"/>
-      <c r="L1" s="115" t="s">
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="33"/>
+      <c r="L1" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
+      <c r="O1" s="143"/>
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
     </row>
     <row r="2" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="135"/>
-      <c r="E2" s="136" t="s">
+      <c r="D2" s="144"/>
+      <c r="E2" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="136"/>
-      <c r="G2" s="137" t="s">
+      <c r="F2" s="145"/>
+      <c r="G2" s="146" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="137"/>
-      <c r="I2" s="38"/>
-      <c r="L2" s="138" t="s">
+      <c r="H2" s="146"/>
+      <c r="I2" s="33"/>
+      <c r="L2" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="135"/>
-      <c r="N2" s="136" t="s">
+      <c r="M2" s="144"/>
+      <c r="N2" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="136"/>
-      <c r="P2" s="137" t="s">
+      <c r="O2" s="145"/>
+      <c r="P2" s="146" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="137"/>
+      <c r="Q2" s="146"/>
       <c r="S2" t="s">
         <v>37</v>
       </c>
@@ -3684,43 +3725,43 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="134"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="28" t="s">
+      <c r="A3" s="142"/>
+      <c r="B3" s="142"/>
+      <c r="C3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="L3" s="36" t="s">
+      <c r="I3" s="33"/>
+      <c r="L3" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="M3" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="P3" s="33" t="s">
+      <c r="P3" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="Q3" s="33" t="s">
+      <c r="Q3" s="28" t="s">
         <v>95</v>
       </c>
       <c r="S3" t="s">
@@ -3745,34 +3786,34 @@
     <row r="4" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="4"/>
-      <c r="C4" s="132" t="s">
+      <c r="C4" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="132"/>
-      <c r="E4" s="120" t="s">
+      <c r="D4" s="148"/>
+      <c r="E4" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="121"/>
-      <c r="G4" s="113" t="s">
+      <c r="F4" s="150"/>
+      <c r="G4" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="38">
+      <c r="H4" s="141"/>
+      <c r="I4" s="33">
         <f>AVERAGE(C5:H8)</f>
         <v>2.8995833333333327</v>
       </c>
-      <c r="L4" s="133" t="s">
+      <c r="L4" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="132"/>
-      <c r="N4" s="120" t="s">
+      <c r="M4" s="148"/>
+      <c r="N4" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="O4" s="121"/>
-      <c r="P4" s="113" t="s">
+      <c r="O4" s="150"/>
+      <c r="P4" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="114"/>
+      <c r="Q4" s="141"/>
       <c r="S4" t="s">
         <v>38</v>
       </c>
@@ -3784,52 +3825,52 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="115">
+      <c r="A5" s="143">
         <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="24">
         <v>3.33</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="24">
         <v>4</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="29">
         <v>2.6</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="29">
         <v>2.6</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="30">
         <v>3.6</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="30">
         <v>3.6</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="L5" s="37">
+      <c r="I5" s="33"/>
+      <c r="L5" s="32">
         <f>C5</f>
         <v>3.33</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="24">
         <f>D5-2+L5</f>
         <v>5.33</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="29">
         <f>E5</f>
         <v>2.6</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="29">
         <f>F5-2+N5</f>
         <v>3.2</v>
       </c>
-      <c r="P5" s="35">
+      <c r="P5" s="30">
         <f>G5</f>
         <v>3.6</v>
       </c>
-      <c r="Q5" s="35">
+      <c r="Q5" s="30">
         <f>H5-2+P5</f>
         <v>5.2</v>
       </c>
@@ -3853,50 +3894,50 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="115"/>
+      <c r="A6" s="143"/>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="24">
         <v>3</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="24">
         <v>4</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="29">
         <v>3</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="29">
         <v>3</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="30">
         <v>3.3</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="30">
         <v>3</v>
       </c>
-      <c r="I6" s="38"/>
-      <c r="L6" s="37">
+      <c r="I6" s="33"/>
+      <c r="L6" s="32">
         <f>C6</f>
         <v>3</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="24">
         <f t="shared" ref="M6:M8" si="0">D6-2+L6</f>
         <v>5</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="29">
         <f>E6</f>
         <v>3</v>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="29">
         <f>F6-2+N6</f>
         <v>4</v>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="30">
         <f>G6</f>
         <v>3.3</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="30">
         <f t="shared" ref="Q6:Q8" si="1">H6-2+P6</f>
         <v>4.3</v>
       </c>
@@ -3920,50 +3961,50 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="115"/>
+      <c r="A7" s="143"/>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="24">
         <v>3</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="24">
         <v>3</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="29">
         <v>2.6</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="30">
         <v>2.6</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="30">
         <v>2.6</v>
       </c>
-      <c r="I7" s="38"/>
-      <c r="L7" s="37">
+      <c r="I7" s="33"/>
+      <c r="L7" s="32">
         <f>C7</f>
         <v>3</v>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="29">
         <f>E7</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="29">
         <f t="shared" ref="O7:O8" si="2">F7-2+N7</f>
         <v>2.9</v>
       </c>
-      <c r="P7" s="35">
+      <c r="P7" s="30">
         <f>G7</f>
         <v>2.6</v>
       </c>
-      <c r="Q7" s="35">
+      <c r="Q7" s="30">
         <f t="shared" si="1"/>
         <v>3.2</v>
       </c>
@@ -3987,50 +4028,50 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="115"/>
+      <c r="A8" s="143"/>
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>2.33</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="24">
         <v>2.33</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="29">
         <v>2.6</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="30">
         <v>2.6</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I8" s="38"/>
-      <c r="L8" s="37">
+      <c r="I8" s="33"/>
+      <c r="L8" s="32">
         <f>C8</f>
         <v>2.33</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="24">
         <f t="shared" si="0"/>
         <v>2.66</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="29">
         <f>E8</f>
         <v>2.6</v>
       </c>
-      <c r="O8" s="34">
+      <c r="O8" s="29">
         <f t="shared" si="2"/>
         <v>2.9</v>
       </c>
-      <c r="P8" s="35">
+      <c r="P8" s="30">
         <f>G8</f>
         <v>2.6</v>
       </c>
-      <c r="Q8" s="35">
+      <c r="Q8" s="30">
         <f t="shared" si="1"/>
         <v>2.9</v>
       </c>
@@ -4055,34 +4096,34 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="C9" s="122" t="s">
+      <c r="C9" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="122"/>
-      <c r="E9" s="120" t="s">
+      <c r="D9" s="152"/>
+      <c r="E9" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="121"/>
-      <c r="G9" s="113" t="s">
+      <c r="F9" s="150"/>
+      <c r="G9" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="114"/>
-      <c r="I9" s="38">
+      <c r="H9" s="141"/>
+      <c r="I9" s="33">
         <f t="shared" ref="I9:I49" si="3">AVERAGE(C10:H13)</f>
         <v>2.5741666666666658</v>
       </c>
-      <c r="L9" s="123" t="s">
+      <c r="L9" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="122"/>
-      <c r="N9" s="120" t="s">
+      <c r="M9" s="152"/>
+      <c r="N9" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="O9" s="121"/>
-      <c r="P9" s="113" t="s">
+      <c r="O9" s="150"/>
+      <c r="P9" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="Q9" s="114"/>
+      <c r="Q9" s="141"/>
       <c r="S9" t="s">
         <v>36</v>
       </c>
@@ -4094,52 +4135,52 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="115">
+      <c r="A10" s="143">
         <v>2</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="24">
         <v>3.33</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="24">
         <v>2.6</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="29">
         <v>2.6</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="29">
         <v>2</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="30">
         <v>3</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="30">
         <v>3</v>
       </c>
-      <c r="I10" s="38"/>
-      <c r="L10" s="37">
+      <c r="I10" s="33"/>
+      <c r="L10" s="32">
         <f>C10-2</f>
         <v>1.33</v>
       </c>
-      <c r="M10" s="29">
+      <c r="M10" s="24">
         <f>D10-2+L10</f>
         <v>1.9300000000000002</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="29">
         <f>E10-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="29">
         <f>F10-2+N10</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="P10" s="35">
+      <c r="P10" s="30">
         <f>G10-2</f>
         <v>1</v>
       </c>
-      <c r="Q10" s="35">
+      <c r="Q10" s="30">
         <f>H10-2+P10</f>
         <v>2</v>
       </c>
@@ -4163,50 +4204,50 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="115"/>
+      <c r="A11" s="143"/>
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="24">
         <v>3.33</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="24">
         <v>2.33</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="29">
         <v>2.6</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="29">
         <v>2.6</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="30">
         <v>3</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="L11" s="37">
+      <c r="I11" s="33"/>
+      <c r="L11" s="32">
         <f>C11-2</f>
         <v>1.33</v>
       </c>
-      <c r="M11" s="29">
+      <c r="M11" s="24">
         <f t="shared" ref="M11:M13" si="4">D11-2+L11</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="29">
         <f>E11-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="29">
         <f t="shared" ref="O11:O13" si="5">F11-2+N11</f>
         <v>1.2000000000000002</v>
       </c>
-      <c r="P11" s="35">
+      <c r="P11" s="30">
         <f>G11-2</f>
         <v>1</v>
       </c>
-      <c r="Q11" s="35">
+      <c r="Q11" s="30">
         <f t="shared" ref="Q11:Q13" si="6">H11-2+P11</f>
         <v>1.2999999999999998</v>
       </c>
@@ -4230,50 +4271,50 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="115"/>
+      <c r="A12" s="143"/>
       <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="24">
         <v>3.33</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="24">
         <v>2.33</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="29">
         <v>2.6</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I12" s="38"/>
-      <c r="L12" s="37">
+      <c r="I12" s="33"/>
+      <c r="L12" s="32">
         <f>C12-2</f>
         <v>1.33</v>
       </c>
-      <c r="M12" s="29">
+      <c r="M12" s="24">
         <f t="shared" si="4"/>
         <v>1.6600000000000001</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="29">
         <f>E12-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="29">
         <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="P12" s="35">
+      <c r="P12" s="30">
         <f>G12-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q12" s="35">
+      <c r="Q12" s="30">
         <f t="shared" si="6"/>
         <v>0.59999999999999964</v>
       </c>
@@ -4297,50 +4338,50 @@
       </c>
     </row>
     <row r="13" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="115"/>
+      <c r="A13" s="143"/>
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="24">
         <v>3.33</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="24">
         <v>2</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="29">
         <v>1.3</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="30">
         <v>3</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="30">
         <v>2</v>
       </c>
-      <c r="I13" s="38"/>
-      <c r="L13" s="37">
+      <c r="I13" s="33"/>
+      <c r="L13" s="32">
         <f>C13-2</f>
         <v>1.33</v>
       </c>
-      <c r="M13" s="29">
+      <c r="M13" s="24">
         <f t="shared" si="4"/>
         <v>1.33</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="29">
         <f>E13-2</f>
         <v>-0.7</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="29">
         <f t="shared" si="5"/>
         <v>-0.40000000000000013</v>
       </c>
-      <c r="P13" s="35">
+      <c r="P13" s="30">
         <f>G13-2</f>
         <v>1</v>
       </c>
-      <c r="Q13" s="35">
+      <c r="Q13" s="30">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4365,34 +4406,34 @@
     </row>
     <row r="14" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="C14" s="132" t="s">
+      <c r="C14" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="132"/>
-      <c r="E14" s="120" t="s">
+      <c r="D14" s="148"/>
+      <c r="E14" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="121"/>
-      <c r="G14" s="113" t="s">
+      <c r="F14" s="150"/>
+      <c r="G14" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="114"/>
-      <c r="I14" s="38">
+      <c r="H14" s="141"/>
+      <c r="I14" s="33">
         <f t="shared" si="3"/>
         <v>2.6812499999999999</v>
       </c>
-      <c r="L14" s="133" t="s">
+      <c r="L14" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="132"/>
-      <c r="N14" s="120" t="s">
+      <c r="M14" s="148"/>
+      <c r="N14" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="O14" s="121"/>
-      <c r="P14" s="113" t="s">
+      <c r="O14" s="150"/>
+      <c r="P14" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="Q14" s="114"/>
+      <c r="Q14" s="141"/>
       <c r="S14" t="s">
         <v>30</v>
       </c>
@@ -4404,52 +4445,52 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="115">
+      <c r="A15" s="143">
         <v>3</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="24">
         <v>3.66</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="24">
         <v>3</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="29">
         <v>2</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="29">
         <v>3.6</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="30">
         <v>2.6</v>
       </c>
-      <c r="I15" s="38"/>
-      <c r="L15" s="37">
+      <c r="I15" s="33"/>
+      <c r="L15" s="32">
         <f>C15-2</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="M15" s="29">
+      <c r="M15" s="24">
         <f>D15-2+L15</f>
         <v>2.66</v>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="29">
         <f>E15-2</f>
         <v>0</v>
       </c>
-      <c r="O15" s="34">
+      <c r="O15" s="29">
         <f>F15-2+N15</f>
         <v>1.6</v>
       </c>
-      <c r="P15" s="35">
+      <c r="P15" s="30">
         <f>G15-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q15" s="35">
+      <c r="Q15" s="30">
         <f>H15-2+P15</f>
         <v>0.89999999999999991</v>
       </c>
@@ -4473,50 +4514,50 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="115"/>
+      <c r="A16" s="143"/>
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="24">
         <v>3</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="24">
         <v>3.33</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="29">
         <v>2.6</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="29">
         <v>3</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="30">
         <v>2.6</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="L16" s="37">
+      <c r="I16" s="33"/>
+      <c r="L16" s="32">
         <f>C16-2</f>
         <v>1</v>
       </c>
-      <c r="M16" s="29">
+      <c r="M16" s="24">
         <f t="shared" ref="M16:M18" si="7">D16-2+L16</f>
         <v>2.33</v>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="29">
         <f>E16-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="29">
         <f t="shared" ref="O16:O18" si="8">F16-2+N16</f>
         <v>1.6</v>
       </c>
-      <c r="P16" s="35">
+      <c r="P16" s="30">
         <f>G16-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="Q16" s="35">
+      <c r="Q16" s="30">
         <f t="shared" ref="Q16:Q18" si="9">H16-2+P16</f>
         <v>0.89999999999999991</v>
       </c>
@@ -4540,50 +4581,50 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="115"/>
+      <c r="A17" s="143"/>
       <c r="B17">
         <v>3</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="24">
         <v>3</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="24">
         <v>3</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="29">
         <v>3</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="29">
         <v>2.6</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I17" s="38"/>
-      <c r="L17" s="37">
+      <c r="I17" s="33"/>
+      <c r="L17" s="32">
         <f>C17-2</f>
         <v>1</v>
       </c>
-      <c r="M17" s="29">
+      <c r="M17" s="24">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="29">
         <f>E17-2</f>
         <v>1</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="29">
         <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
-      <c r="P17" s="35">
+      <c r="P17" s="30">
         <f>G17-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q17" s="35">
+      <c r="Q17" s="30">
         <f t="shared" si="9"/>
         <v>0.59999999999999964</v>
       </c>
@@ -4607,50 +4648,50 @@
       </c>
     </row>
     <row r="18" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="115"/>
+      <c r="A18" s="143"/>
       <c r="B18">
         <v>4</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="25">
         <v>2.33</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="24">
         <v>2.33</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="29">
         <v>3.6</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="30">
         <v>1.6</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="30">
         <v>2</v>
       </c>
-      <c r="I18" s="38"/>
-      <c r="L18" s="37">
+      <c r="I18" s="33"/>
+      <c r="L18" s="32">
         <f>C18-2</f>
         <v>0.33000000000000007</v>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="24">
         <f t="shared" si="7"/>
         <v>0.66000000000000014</v>
       </c>
-      <c r="N18" s="34">
+      <c r="N18" s="29">
         <f>E18-2</f>
         <v>1.6</v>
       </c>
-      <c r="O18" s="34">
+      <c r="O18" s="29">
         <f t="shared" si="8"/>
         <v>1.9</v>
       </c>
-      <c r="P18" s="35">
+      <c r="P18" s="30">
         <f>G18-2</f>
         <v>-0.39999999999999991</v>
       </c>
-      <c r="Q18" s="35">
+      <c r="Q18" s="30">
         <f t="shared" si="9"/>
         <v>-0.39999999999999991</v>
       </c>
@@ -4675,34 +4716,34 @@
     </row>
     <row r="19" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="C19" s="132" t="s">
+      <c r="C19" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="132"/>
-      <c r="E19" s="127" t="s">
+      <c r="D19" s="148"/>
+      <c r="E19" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="128"/>
-      <c r="G19" s="124" t="s">
+      <c r="F19" s="155"/>
+      <c r="G19" s="156" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="125"/>
-      <c r="I19" s="38">
+      <c r="H19" s="157"/>
+      <c r="I19" s="33">
         <f t="shared" si="3"/>
         <v>2.7395833333333335</v>
       </c>
-      <c r="L19" s="133" t="s">
+      <c r="L19" s="151" t="s">
         <v>35</v>
       </c>
-      <c r="M19" s="132"/>
-      <c r="N19" s="127" t="s">
+      <c r="M19" s="148"/>
+      <c r="N19" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="O19" s="128"/>
-      <c r="P19" s="124" t="s">
+      <c r="O19" s="155"/>
+      <c r="P19" s="156" t="s">
         <v>86</v>
       </c>
-      <c r="Q19" s="125"/>
+      <c r="Q19" s="157"/>
       <c r="S19" t="s">
         <v>35</v>
       </c>
@@ -4714,52 +4755,52 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="115">
+      <c r="A20" s="143">
         <v>4</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="24">
         <v>3.33</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="24">
         <v>4</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="29">
         <v>3.6</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="29">
         <v>4</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I20" s="38"/>
-      <c r="L20" s="37">
+      <c r="I20" s="33"/>
+      <c r="L20" s="32">
         <f>C20-2</f>
         <v>1.33</v>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="24">
         <f>D20-2+L20</f>
         <v>3.33</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="29">
         <f>E20-2</f>
         <v>1.6</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="29">
         <f>F20-2+N20</f>
         <v>3.6</v>
       </c>
-      <c r="P20" s="35">
+      <c r="P20" s="30">
         <f>G20-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q20" s="35">
+      <c r="Q20" s="30">
         <f>H20-2+P20</f>
         <v>0.59999999999999964</v>
       </c>
@@ -4783,50 +4824,50 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="115"/>
+      <c r="A21" s="143"/>
       <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="24">
         <v>3.33</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="24">
         <v>2.33</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="29">
         <v>3.3</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="30">
         <v>1.6</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="L21" s="37">
+      <c r="I21" s="33"/>
+      <c r="L21" s="32">
         <f>C21-2</f>
         <v>1.33</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="24">
         <f t="shared" ref="M21:M23" si="10">D21-2+L21</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="29">
         <f>E21-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="O21" s="34">
+      <c r="O21" s="29">
         <f t="shared" ref="O21:O23" si="11">F21-2+N21</f>
         <v>1.5999999999999996</v>
       </c>
-      <c r="P21" s="35">
+      <c r="P21" s="30">
         <f>G21-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q21" s="35">
+      <c r="Q21" s="30">
         <f t="shared" ref="Q21:Q23" si="12">H21-2+P21</f>
         <v>-0.10000000000000009</v>
       </c>
@@ -4850,50 +4891,50 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="115"/>
+      <c r="A22" s="143"/>
       <c r="B22">
         <v>3</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="24">
         <v>4</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="24">
         <v>2.33</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="29">
         <v>2.6</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="30">
         <v>1.6</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I22" s="38"/>
-      <c r="L22" s="37">
+      <c r="I22" s="33"/>
+      <c r="L22" s="32">
         <f>C22-2</f>
         <v>2</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="24">
         <f t="shared" si="10"/>
         <v>2.33</v>
       </c>
-      <c r="N22" s="34">
+      <c r="N22" s="29">
         <f>E22-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O22" s="34">
+      <c r="O22" s="29">
         <f t="shared" si="11"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="P22" s="35">
+      <c r="P22" s="30">
         <f>G22-2</f>
         <v>-0.39999999999999991</v>
       </c>
-      <c r="Q22" s="35">
+      <c r="Q22" s="30">
         <f t="shared" si="12"/>
         <v>-0.10000000000000009</v>
       </c>
@@ -4917,50 +4958,50 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="115"/>
+      <c r="A23" s="143"/>
       <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="25">
         <v>3.33</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="24">
         <v>2</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="29">
         <v>4</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="29">
         <v>2</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="30">
         <v>2.6</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="30">
         <v>2</v>
       </c>
-      <c r="I23" s="38"/>
-      <c r="L23" s="37">
+      <c r="I23" s="33"/>
+      <c r="L23" s="32">
         <f>C23-2</f>
         <v>1.33</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="24">
         <f t="shared" si="10"/>
         <v>1.33</v>
       </c>
-      <c r="N23" s="34">
+      <c r="N23" s="29">
         <f>E23-2</f>
         <v>2</v>
       </c>
-      <c r="O23" s="34">
+      <c r="O23" s="29">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="P23" s="35">
+      <c r="P23" s="30">
         <f>G23-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="Q23" s="35">
+      <c r="Q23" s="30">
         <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
@@ -4985,34 +5026,34 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="C24" s="122" t="s">
+      <c r="C24" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="127" t="s">
+      <c r="D24" s="152"/>
+      <c r="E24" s="154" t="s">
         <v>80</v>
       </c>
-      <c r="F24" s="128"/>
-      <c r="G24" s="124" t="s">
+      <c r="F24" s="155"/>
+      <c r="G24" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="125"/>
-      <c r="I24" s="38">
+      <c r="H24" s="157"/>
+      <c r="I24" s="33">
         <f t="shared" si="3"/>
         <v>2.8404166666666661</v>
       </c>
-      <c r="L24" s="123" t="s">
+      <c r="L24" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="M24" s="122"/>
-      <c r="N24" s="127" t="s">
+      <c r="M24" s="152"/>
+      <c r="N24" s="154" t="s">
         <v>80</v>
       </c>
-      <c r="O24" s="128"/>
-      <c r="P24" s="124" t="s">
+      <c r="O24" s="155"/>
+      <c r="P24" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="Q24" s="125"/>
+      <c r="Q24" s="157"/>
       <c r="S24" t="s">
         <v>39</v>
       </c>
@@ -5024,52 +5065,52 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="115">
+      <c r="A25" s="143">
         <v>5</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="24">
         <v>3.66</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="24">
         <v>3.33</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="29">
         <v>3</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="29">
         <v>3.6</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="30">
         <v>3</v>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="30">
         <v>1.6</v>
       </c>
-      <c r="I25" s="38"/>
-      <c r="L25" s="37">
+      <c r="I25" s="33"/>
+      <c r="L25" s="32">
         <f>C25-2</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="24">
         <f>D25-2+L25</f>
         <v>2.99</v>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="29">
         <f>E25-2</f>
         <v>1</v>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="29">
         <f>F25-2+N25</f>
         <v>2.6</v>
       </c>
-      <c r="P25" s="35">
+      <c r="P25" s="30">
         <f>G25-2</f>
         <v>1</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="30">
         <f>H25-2+P25</f>
         <v>0.60000000000000009</v>
       </c>
@@ -5093,50 +5134,50 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A26" s="115"/>
+      <c r="A26" s="143"/>
       <c r="B26">
         <v>2</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="24">
         <v>3.66</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="24">
         <v>3.66</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="29">
         <v>3</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="29">
         <v>2.6</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="30">
         <v>3</v>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I26" s="38"/>
-      <c r="L26" s="37">
+      <c r="I26" s="33"/>
+      <c r="L26" s="32">
         <f>C26-2</f>
         <v>1.6600000000000001</v>
       </c>
-      <c r="M26" s="29">
+      <c r="M26" s="24">
         <f t="shared" ref="M26:M28" si="13">D26-2+L26</f>
         <v>3.3200000000000003</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="29">
         <f>E26-2</f>
         <v>1</v>
       </c>
-      <c r="O26" s="34">
+      <c r="O26" s="29">
         <f t="shared" ref="O26:O28" si="14">F26-2+N26</f>
         <v>1.6</v>
       </c>
-      <c r="P26" s="35">
+      <c r="P26" s="30">
         <f>G26-2</f>
         <v>1</v>
       </c>
-      <c r="Q26" s="35">
+      <c r="Q26" s="30">
         <f t="shared" ref="Q26:Q28" si="15">H26-2+P26</f>
         <v>1.2999999999999998</v>
       </c>
@@ -5160,50 +5201,50 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="115"/>
+      <c r="A27" s="143"/>
       <c r="B27">
         <v>3</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="24">
         <v>3</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="24">
         <v>3</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="29">
         <v>3.6</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="29">
         <v>2.6</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I27" s="38"/>
-      <c r="L27" s="37">
+      <c r="I27" s="33"/>
+      <c r="L27" s="32">
         <f>C27-2</f>
         <v>1</v>
       </c>
-      <c r="M27" s="29">
+      <c r="M27" s="24">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="29">
         <f>E27-2</f>
         <v>1.6</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="29">
         <f t="shared" si="14"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="30">
         <f>G27-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="30">
         <f t="shared" si="15"/>
         <v>0.59999999999999964</v>
       </c>
@@ -5227,50 +5268,50 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="115"/>
+      <c r="A28" s="143"/>
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="24">
         <v>2.33</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="24">
         <v>2.33</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="29">
         <v>4</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="30">
         <v>2</v>
       </c>
-      <c r="H28" s="35">
+      <c r="H28" s="30">
         <v>2</v>
       </c>
-      <c r="I28" s="38"/>
-      <c r="L28" s="37">
+      <c r="I28" s="33"/>
+      <c r="L28" s="32">
         <f>C28-2</f>
         <v>0.33000000000000007</v>
       </c>
-      <c r="M28" s="29">
+      <c r="M28" s="24">
         <f t="shared" si="13"/>
         <v>0.66000000000000014</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="29">
         <f>E28-2</f>
         <v>2</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="29">
         <f t="shared" si="14"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="P28" s="35">
+      <c r="P28" s="30">
         <f>G28-2</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="35">
+      <c r="Q28" s="30">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
@@ -5295,34 +5336,34 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
-      <c r="C29" s="122" t="s">
+      <c r="C29" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="131" t="s">
+      <c r="D29" s="152"/>
+      <c r="E29" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="131"/>
-      <c r="G29" s="130" t="s">
+      <c r="F29" s="158"/>
+      <c r="G29" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="130"/>
-      <c r="I29" s="38">
+      <c r="H29" s="159"/>
+      <c r="I29" s="33">
         <f t="shared" si="3"/>
         <v>2.7816666666666658</v>
       </c>
-      <c r="L29" s="123" t="s">
+      <c r="L29" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="M29" s="122"/>
-      <c r="N29" s="131" t="s">
+      <c r="M29" s="152"/>
+      <c r="N29" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="O29" s="131"/>
-      <c r="P29" s="130" t="s">
+      <c r="O29" s="158"/>
+      <c r="P29" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="Q29" s="130"/>
+      <c r="Q29" s="159"/>
       <c r="S29" t="s">
         <v>40</v>
       </c>
@@ -5334,52 +5375,52 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="115">
+      <c r="A30" s="143">
         <v>6</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="24">
         <v>3.3</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="24">
         <v>4</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="29">
         <v>3.6</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="29">
         <v>4</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="30">
         <v>2</v>
       </c>
-      <c r="I30" s="38"/>
-      <c r="L30" s="37">
+      <c r="I30" s="33"/>
+      <c r="L30" s="32">
         <f>C30-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="24">
         <f>D30-2+L30</f>
         <v>3.3</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="29">
         <f>E30-2</f>
         <v>1.6</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="29">
         <f>F30-2+N30</f>
         <v>3.6</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="30">
         <f>G30-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="30">
         <f>H30-2+P30</f>
         <v>0.29999999999999982</v>
       </c>
@@ -5403,50 +5444,50 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A31" s="115"/>
+      <c r="A31" s="143"/>
       <c r="B31">
         <v>2</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="24">
         <v>3.3</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="24">
         <v>4</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="29">
         <v>3</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="30">
         <v>2.6</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I31" s="38"/>
-      <c r="L31" s="37">
+      <c r="I31" s="33"/>
+      <c r="L31" s="32">
         <f>C31-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="M31" s="29">
+      <c r="M31" s="24">
         <f t="shared" ref="M31:M33" si="16">D31-2+L31</f>
         <v>3.3</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="29">
         <f>E31-2</f>
         <v>1</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="29">
         <f t="shared" ref="O31:O33" si="17">F31-2+N31</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="30">
         <f>G31-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="30">
         <f t="shared" ref="Q31:Q33" si="18">H31-2+P31</f>
         <v>0.89999999999999991</v>
       </c>
@@ -5470,50 +5511,50 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A32" s="115"/>
+      <c r="A32" s="143"/>
       <c r="B32">
         <v>3</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="24">
         <v>3.3</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="24">
         <v>3</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E32" s="29">
         <v>3.6</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I32" s="38"/>
-      <c r="L32" s="37">
+      <c r="I32" s="33"/>
+      <c r="L32" s="32">
         <f>C32-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="M32" s="29">
+      <c r="M32" s="24">
         <f t="shared" si="16"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="N32" s="34">
+      <c r="N32" s="29">
         <f>E32-2</f>
         <v>1.6</v>
       </c>
-      <c r="O32" s="34">
+      <c r="O32" s="29">
         <f t="shared" si="17"/>
         <v>1.9</v>
       </c>
-      <c r="P32" s="35">
+      <c r="P32" s="30">
         <f>G32-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q32" s="35">
+      <c r="Q32" s="30">
         <f t="shared" si="18"/>
         <v>0.59999999999999964</v>
       </c>
@@ -5537,50 +5578,50 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A33" s="115"/>
+      <c r="A33" s="143"/>
       <c r="B33">
         <v>4</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="24">
         <v>2.33</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="29">
         <v>3.33</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="29">
         <v>2</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="30">
         <v>1.3</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="30">
         <v>2</v>
       </c>
-      <c r="I33" s="38"/>
-      <c r="L33" s="37">
+      <c r="I33" s="33"/>
+      <c r="L33" s="32">
         <f>C33-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="M33" s="29">
+      <c r="M33" s="24">
         <f t="shared" si="16"/>
         <v>0.62999999999999989</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="29">
         <f>E33-2</f>
         <v>1.33</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="29">
         <f t="shared" si="17"/>
         <v>1.33</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="30">
         <f>G33-2</f>
         <v>-0.7</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="30">
         <f t="shared" si="18"/>
         <v>-0.7</v>
       </c>
@@ -5605,34 +5646,34 @@
     </row>
     <row r="34" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
-      <c r="C34" s="122" t="s">
+      <c r="C34" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="122"/>
-      <c r="E34" s="120" t="s">
+      <c r="D34" s="152"/>
+      <c r="E34" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="121"/>
-      <c r="G34" s="113" t="s">
+      <c r="F34" s="150"/>
+      <c r="G34" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="H34" s="114"/>
-      <c r="I34" s="38">
+      <c r="H34" s="141"/>
+      <c r="I34" s="33">
         <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
-      <c r="L34" s="123" t="s">
+      <c r="L34" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="M34" s="122"/>
-      <c r="N34" s="120" t="s">
+      <c r="M34" s="152"/>
+      <c r="N34" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="O34" s="121"/>
-      <c r="P34" s="113" t="s">
+      <c r="O34" s="150"/>
+      <c r="P34" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="Q34" s="114"/>
+      <c r="Q34" s="141"/>
       <c r="S34" t="s">
         <v>45</v>
       </c>
@@ -5644,52 +5685,52 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A35" s="115">
+      <c r="A35" s="143">
         <v>7</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="24">
         <v>3</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="29">
         <v>3.6</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="29">
         <v>3.6</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I35" s="38"/>
-      <c r="L35" s="37">
+      <c r="I35" s="33"/>
+      <c r="L35" s="32">
         <f>C35-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="M35" s="29">
+      <c r="M35" s="24">
         <f>D35-2+L35</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="29">
         <f>E35-2</f>
         <v>1.6</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="29">
         <f>F35-2+N35</f>
         <v>3.2</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="30">
         <f>G35-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="30">
         <f>H35-2+P35</f>
         <v>0.59999999999999964</v>
       </c>
@@ -5713,50 +5754,50 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A36" s="115"/>
+      <c r="A36" s="143"/>
       <c r="B36">
         <v>2</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="24">
         <v>2.6</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="29">
         <v>3.3</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="29">
         <v>3</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I36" s="38"/>
-      <c r="L36" s="37">
+      <c r="I36" s="33"/>
+      <c r="L36" s="32">
         <f>C36-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="M36" s="29">
+      <c r="M36" s="24">
         <f t="shared" ref="M36:M38" si="19">D36-2+L36</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="29">
         <f>E36-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="29">
         <f t="shared" ref="O36:O38" si="20">F36-2+N36</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="30">
         <f>G36-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="30">
         <f t="shared" ref="Q36:Q38" si="21">H36-2+P36</f>
         <v>0.59999999999999964</v>
       </c>
@@ -5780,50 +5821,50 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A37" s="115"/>
+      <c r="A37" s="143"/>
       <c r="B37">
         <v>3</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="24">
         <v>3.3</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="24">
         <v>2.6</v>
       </c>
-      <c r="E37" s="34">
+      <c r="E37" s="29">
         <v>2.6</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="29">
         <v>2.6</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="30">
         <v>2</v>
       </c>
-      <c r="H37" s="35">
+      <c r="H37" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I37" s="38"/>
-      <c r="L37" s="37">
+      <c r="I37" s="33"/>
+      <c r="L37" s="32">
         <f>C37-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="M37" s="29">
+      <c r="M37" s="24">
         <f t="shared" si="19"/>
         <v>1.9</v>
       </c>
-      <c r="N37" s="34">
+      <c r="N37" s="29">
         <f>E37-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O37" s="34">
+      <c r="O37" s="29">
         <f t="shared" si="20"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="P37" s="35">
+      <c r="P37" s="30">
         <f>G37-2</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="35">
+      <c r="Q37" s="30">
         <f t="shared" si="21"/>
         <v>0.29999999999999982</v>
       </c>
@@ -5847,50 +5888,50 @@
       </c>
     </row>
     <row r="38" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="115"/>
+      <c r="A38" s="143"/>
       <c r="B38">
         <v>4</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="29">
         <v>3.6</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G38" s="35">
+      <c r="G38" s="30">
         <v>1.6</v>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="30">
         <v>2</v>
       </c>
-      <c r="I38" s="38"/>
-      <c r="L38" s="37">
+      <c r="I38" s="33"/>
+      <c r="L38" s="32">
         <f>C38-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="M38" s="29">
+      <c r="M38" s="24">
         <f t="shared" si="19"/>
         <v>0.59999999999999964</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="29">
         <f>E38-2</f>
         <v>1.6</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="29">
         <f t="shared" si="20"/>
         <v>1.9</v>
       </c>
-      <c r="P38" s="35">
+      <c r="P38" s="30">
         <f>G38-2</f>
         <v>-0.39999999999999991</v>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="30">
         <f t="shared" si="21"/>
         <v>-0.39999999999999991</v>
       </c>
@@ -5915,34 +5956,34 @@
     </row>
     <row r="39" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
-      <c r="C39" s="126" t="s">
+      <c r="C39" s="160" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="126"/>
-      <c r="E39" s="120" t="s">
+      <c r="D39" s="160"/>
+      <c r="E39" s="149" t="s">
         <v>76</v>
       </c>
-      <c r="F39" s="121"/>
-      <c r="G39" s="124" t="s">
+      <c r="F39" s="150"/>
+      <c r="G39" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="H39" s="125"/>
-      <c r="I39" s="38">
+      <c r="H39" s="157"/>
+      <c r="I39" s="33">
         <f t="shared" si="3"/>
         <v>2.6875</v>
       </c>
-      <c r="L39" s="129" t="s">
+      <c r="L39" s="161" t="s">
         <v>77</v>
       </c>
-      <c r="M39" s="126"/>
-      <c r="N39" s="120" t="s">
+      <c r="M39" s="160"/>
+      <c r="N39" s="149" t="s">
         <v>76</v>
       </c>
-      <c r="O39" s="121"/>
-      <c r="P39" s="124" t="s">
+      <c r="O39" s="150"/>
+      <c r="P39" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="Q39" s="125"/>
+      <c r="Q39" s="157"/>
       <c r="S39" t="s">
         <v>77</v>
       </c>
@@ -5954,52 +5995,52 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A40" s="115">
+      <c r="A40" s="143">
         <v>8</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="24">
         <v>2.6</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="24">
         <v>3.6</v>
       </c>
-      <c r="E40" s="34">
+      <c r="E40" s="29">
         <v>2.6</v>
       </c>
-      <c r="F40" s="34">
+      <c r="F40" s="29">
         <v>3.3</v>
       </c>
-      <c r="G40" s="35">
+      <c r="G40" s="30">
         <v>3</v>
       </c>
-      <c r="H40" s="35">
+      <c r="H40" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I40" s="38"/>
-      <c r="L40" s="37">
+      <c r="I40" s="33"/>
+      <c r="L40" s="32">
         <f>C40-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="M40" s="29">
+      <c r="M40" s="24">
         <f>D40-2+L40</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="N40" s="34">
+      <c r="N40" s="29">
         <f>E40-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O40" s="34">
+      <c r="O40" s="29">
         <f>F40-2+N40</f>
         <v>1.9</v>
       </c>
-      <c r="P40" s="35">
+      <c r="P40" s="30">
         <f>G40-2</f>
         <v>1</v>
       </c>
-      <c r="Q40" s="35">
+      <c r="Q40" s="30">
         <f>H40-2+P40</f>
         <v>1.2999999999999998</v>
       </c>
@@ -6023,50 +6064,50 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A41" s="115"/>
+      <c r="A41" s="143"/>
       <c r="B41">
         <v>2</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="24">
         <v>2.6</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="29">
         <v>3</v>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="30">
         <v>3</v>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="30">
         <v>2.6</v>
       </c>
-      <c r="I41" s="38"/>
-      <c r="L41" s="37">
+      <c r="I41" s="33"/>
+      <c r="L41" s="32">
         <f>C41-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="M41" s="29">
+      <c r="M41" s="24">
         <f t="shared" ref="M41:M43" si="22">D41-2+L41</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="29">
         <f>E41-2</f>
         <v>0.29999999999999982</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="29">
         <f t="shared" ref="O41:O43" si="23">F41-2+N41</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="P41" s="35">
+      <c r="P41" s="30">
         <f>G41-2</f>
         <v>1</v>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="30">
         <f t="shared" ref="Q41:Q43" si="24">H41-2+P41</f>
         <v>1.6</v>
       </c>
@@ -6090,50 +6131,50 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A42" s="115"/>
+      <c r="A42" s="143"/>
       <c r="B42">
         <v>3</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="24">
         <v>3.6</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="29">
         <v>3.3</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="29">
         <v>2.6</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="30">
         <v>3</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="30">
         <v>2.6</v>
       </c>
-      <c r="I42" s="38"/>
-      <c r="L42" s="37">
+      <c r="I42" s="33"/>
+      <c r="L42" s="32">
         <f>C42-2</f>
         <v>1.6</v>
       </c>
-      <c r="M42" s="29">
+      <c r="M42" s="24">
         <f t="shared" si="22"/>
         <v>1.9</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="29">
         <f>E42-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="29">
         <f t="shared" si="23"/>
         <v>1.9</v>
       </c>
-      <c r="P42" s="35">
+      <c r="P42" s="30">
         <f>G42-2</f>
         <v>1</v>
       </c>
-      <c r="Q42" s="35">
+      <c r="Q42" s="30">
         <f t="shared" si="24"/>
         <v>1.6</v>
       </c>
@@ -6157,50 +6198,50 @@
       </c>
     </row>
     <row r="43" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="115"/>
+      <c r="A43" s="143"/>
       <c r="B43">
         <v>4</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="25">
         <v>3</v>
       </c>
-      <c r="D43" s="29">
+      <c r="D43" s="24">
         <v>2</v>
       </c>
-      <c r="E43" s="34">
+      <c r="E43" s="29">
         <v>3.3</v>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G43" s="35">
+      <c r="G43" s="30">
         <v>1</v>
       </c>
-      <c r="H43" s="35">
+      <c r="H43" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I43" s="38"/>
-      <c r="L43" s="37">
+      <c r="I43" s="33"/>
+      <c r="L43" s="32">
         <f>C43-2</f>
         <v>1</v>
       </c>
-      <c r="M43" s="29">
+      <c r="M43" s="24">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="N43" s="34">
+      <c r="N43" s="29">
         <f>E43-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="O43" s="34">
+      <c r="O43" s="29">
         <f t="shared" si="23"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="P43" s="35">
+      <c r="P43" s="30">
         <f>G43-2</f>
         <v>-1</v>
       </c>
-      <c r="Q43" s="35">
+      <c r="Q43" s="30">
         <f t="shared" si="24"/>
         <v>-0.70000000000000018</v>
       </c>
@@ -6225,34 +6266,34 @@
     </row>
     <row r="44" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="C44" s="126" t="s">
+      <c r="C44" s="160" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="126"/>
-      <c r="E44" s="127" t="s">
+      <c r="D44" s="160"/>
+      <c r="E44" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="F44" s="128"/>
-      <c r="G44" s="124" t="s">
+      <c r="F44" s="155"/>
+      <c r="G44" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="H44" s="125"/>
-      <c r="I44" s="38">
+      <c r="H44" s="157"/>
+      <c r="I44" s="33">
         <f t="shared" si="3"/>
         <v>2.9874999999999994</v>
       </c>
-      <c r="L44" s="129" t="s">
+      <c r="L44" s="161" t="s">
         <v>84</v>
       </c>
-      <c r="M44" s="126"/>
-      <c r="N44" s="127" t="s">
+      <c r="M44" s="160"/>
+      <c r="N44" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="O44" s="128"/>
-      <c r="P44" s="124" t="s">
+      <c r="O44" s="155"/>
+      <c r="P44" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="Q44" s="125"/>
+      <c r="Q44" s="157"/>
       <c r="S44" t="s">
         <v>84</v>
       </c>
@@ -6264,52 +6305,52 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A45" s="115">
+      <c r="A45" s="143">
         <v>9</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="24">
         <v>3.6</v>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="24">
         <v>4</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="29">
         <v>3.3</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="29">
         <v>3.6</v>
       </c>
-      <c r="G45" s="35">
+      <c r="G45" s="30">
         <v>3</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="30">
         <v>2</v>
       </c>
-      <c r="I45" s="38"/>
-      <c r="L45" s="37">
+      <c r="I45" s="33"/>
+      <c r="L45" s="32">
         <f>C45-2</f>
         <v>1.6</v>
       </c>
-      <c r="M45" s="29">
+      <c r="M45" s="24">
         <f>D45-2+L45</f>
         <v>3.6</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="29">
         <f>E45-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="29">
         <f>F45-2+N45</f>
         <v>2.9</v>
       </c>
-      <c r="P45" s="35">
+      <c r="P45" s="30">
         <f>G45-2</f>
         <v>1</v>
       </c>
-      <c r="Q45" s="35">
+      <c r="Q45" s="30">
         <f>H45-2+P45</f>
         <v>1</v>
       </c>
@@ -6333,50 +6374,50 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A46" s="115"/>
+      <c r="A46" s="143"/>
       <c r="B46">
         <v>2</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="24">
         <v>3</v>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E46" s="34">
+      <c r="E46" s="29">
         <v>3.3</v>
       </c>
-      <c r="F46" s="34">
+      <c r="F46" s="29">
         <v>3.3</v>
       </c>
-      <c r="G46" s="35">
+      <c r="G46" s="30">
         <v>3</v>
       </c>
-      <c r="H46" s="35">
+      <c r="H46" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I46" s="38"/>
-      <c r="L46" s="37">
+      <c r="I46" s="33"/>
+      <c r="L46" s="32">
         <f>C46-2</f>
         <v>1</v>
       </c>
-      <c r="M46" s="29">
+      <c r="M46" s="24">
         <f t="shared" ref="M46:M48" si="25">D46-2+L46</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="N46" s="34">
+      <c r="N46" s="29">
         <f>E46-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="O46" s="34">
+      <c r="O46" s="29">
         <f t="shared" ref="O46:O48" si="26">F46-2+N46</f>
         <v>2.5999999999999996</v>
       </c>
-      <c r="P46" s="35">
+      <c r="P46" s="30">
         <f>G46-2</f>
         <v>1</v>
       </c>
-      <c r="Q46" s="35">
+      <c r="Q46" s="30">
         <f t="shared" ref="Q46:Q48" si="27">H46-2+P46</f>
         <v>1.2999999999999998</v>
       </c>
@@ -6400,50 +6441,50 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A47" s="115"/>
+      <c r="A47" s="143"/>
       <c r="B47">
         <v>3</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="24">
         <v>2.6</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E47" s="34">
+      <c r="E47" s="29">
         <v>3.6</v>
       </c>
-      <c r="F47" s="34">
+      <c r="F47" s="29">
         <v>3</v>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="30">
         <v>3</v>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I47" s="38"/>
-      <c r="L47" s="37">
+      <c r="I47" s="33"/>
+      <c r="L47" s="32">
         <f>C47-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="M47" s="29">
+      <c r="M47" s="24">
         <f t="shared" si="25"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="N47" s="34">
+      <c r="N47" s="29">
         <f>E47-2</f>
         <v>1.6</v>
       </c>
-      <c r="O47" s="34">
+      <c r="O47" s="29">
         <f t="shared" si="26"/>
         <v>2.6</v>
       </c>
-      <c r="P47" s="35">
+      <c r="P47" s="30">
         <f>G47-2</f>
         <v>1</v>
       </c>
-      <c r="Q47" s="35">
+      <c r="Q47" s="30">
         <f t="shared" si="27"/>
         <v>1.2999999999999998</v>
       </c>
@@ -6467,50 +6508,50 @@
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A48" s="115"/>
+      <c r="A48" s="143"/>
       <c r="B48">
         <v>4</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="24">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="24">
         <v>2</v>
       </c>
-      <c r="E48" s="34">
+      <c r="E48" s="29">
         <v>4</v>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G48" s="35">
+      <c r="G48" s="30">
         <v>3.3</v>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="30">
         <v>2</v>
       </c>
-      <c r="I48" s="38"/>
-      <c r="L48" s="37">
+      <c r="I48" s="33"/>
+      <c r="L48" s="32">
         <f>C48-2</f>
         <v>2.5999999999999996</v>
       </c>
-      <c r="M48" s="29">
+      <c r="M48" s="24">
         <f t="shared" si="25"/>
         <v>2.5999999999999996</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="29">
         <f>E48-2</f>
         <v>2</v>
       </c>
-      <c r="O48" s="34">
+      <c r="O48" s="29">
         <f t="shared" si="26"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="P48" s="35">
+      <c r="P48" s="30">
         <f>G48-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="Q48" s="35">
+      <c r="Q48" s="30">
         <f t="shared" si="27"/>
         <v>1.2999999999999998</v>
       </c>
@@ -6535,34 +6576,34 @@
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
-      <c r="C49" s="122" t="s">
+      <c r="C49" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="122"/>
-      <c r="E49" s="120" t="s">
+      <c r="D49" s="152"/>
+      <c r="E49" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="F49" s="121"/>
-      <c r="G49" s="113" t="s">
+      <c r="F49" s="150"/>
+      <c r="G49" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="H49" s="114"/>
-      <c r="I49" s="38">
+      <c r="H49" s="141"/>
+      <c r="I49" s="33">
         <f t="shared" si="3"/>
         <v>3.0166666666666662</v>
       </c>
-      <c r="L49" s="123" t="s">
+      <c r="L49" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="M49" s="122"/>
-      <c r="N49" s="120" t="s">
+      <c r="M49" s="152"/>
+      <c r="N49" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="O49" s="121"/>
-      <c r="P49" s="113" t="s">
+      <c r="O49" s="150"/>
+      <c r="P49" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="Q49" s="114"/>
+      <c r="Q49" s="141"/>
       <c r="S49" t="s">
         <v>89</v>
       </c>
@@ -6574,52 +6615,52 @@
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A50" s="115">
+      <c r="A50" s="143">
         <v>10</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="24">
         <v>3.6</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="24">
         <v>4</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="29">
         <v>3</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="29">
         <v>4</v>
       </c>
-      <c r="G50" s="35">
+      <c r="G50" s="30">
         <v>3</v>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="30">
         <v>4</v>
       </c>
-      <c r="I50" s="38"/>
-      <c r="L50" s="37">
+      <c r="I50" s="33"/>
+      <c r="L50" s="32">
         <f>C50-2</f>
         <v>1.6</v>
       </c>
-      <c r="M50" s="29">
+      <c r="M50" s="24">
         <f>D50-2+L50</f>
         <v>3.6</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="29">
         <f>E50-2</f>
         <v>1</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="29">
         <f>F50-2+N50</f>
         <v>3</v>
       </c>
-      <c r="P50" s="35">
+      <c r="P50" s="30">
         <f>G50-2</f>
         <v>1</v>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="30">
         <f>H50-2+P50</f>
         <v>3</v>
       </c>
@@ -6643,50 +6684,50 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A51" s="115"/>
+      <c r="A51" s="143"/>
       <c r="B51">
         <v>2</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="24">
         <v>3.6</v>
       </c>
-      <c r="D51" s="29">
+      <c r="D51" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="29">
         <v>3</v>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="29">
         <v>2.6</v>
       </c>
-      <c r="G51" s="35">
+      <c r="G51" s="30">
         <v>3</v>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I51" s="38"/>
-      <c r="L51" s="37">
+      <c r="I51" s="33"/>
+      <c r="L51" s="32">
         <f>C51-2</f>
         <v>1.6</v>
       </c>
-      <c r="M51" s="29">
+      <c r="M51" s="24">
         <f t="shared" ref="M51:M53" si="28">D51-2+L51</f>
         <v>1.9</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="29">
         <f>E51-2</f>
         <v>1</v>
       </c>
-      <c r="O51" s="34">
+      <c r="O51" s="29">
         <f t="shared" ref="O51:O53" si="29">F51-2+N51</f>
         <v>1.6</v>
       </c>
-      <c r="P51" s="35">
+      <c r="P51" s="30">
         <f>G51-2</f>
         <v>1</v>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="30">
         <f t="shared" ref="Q51:Q53" si="30">H51-2+P51</f>
         <v>1.2999999999999998</v>
       </c>
@@ -6710,50 +6751,50 @@
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A52" s="115"/>
+      <c r="A52" s="143"/>
       <c r="B52">
         <v>3</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="24">
         <v>3.3</v>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="24">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E52" s="34">
+      <c r="E52" s="29">
         <v>2.6</v>
       </c>
-      <c r="F52" s="34">
+      <c r="F52" s="29">
         <v>2.6</v>
       </c>
-      <c r="G52" s="35">
+      <c r="G52" s="30">
         <v>2.6</v>
       </c>
-      <c r="H52" s="35">
+      <c r="H52" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I52" s="38"/>
-      <c r="L52" s="37">
+      <c r="I52" s="33"/>
+      <c r="L52" s="32">
         <f>C52-2</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="M52" s="29">
+      <c r="M52" s="24">
         <f t="shared" si="28"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="N52" s="34">
+      <c r="N52" s="29">
         <f>E52-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O52" s="34">
+      <c r="O52" s="29">
         <f t="shared" si="29"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="P52" s="35">
+      <c r="P52" s="30">
         <f>G52-2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="Q52" s="35">
+      <c r="Q52" s="30">
         <f t="shared" si="30"/>
         <v>0.89999999999999991</v>
       </c>
@@ -6777,50 +6818,50 @@
       </c>
     </row>
     <row r="53" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="115"/>
+      <c r="A53" s="143"/>
       <c r="B53">
         <v>4</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="24">
         <v>4</v>
       </c>
-      <c r="D53" s="29">
+      <c r="D53" s="24">
         <v>2</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="29">
         <v>4</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G53" s="35">
+      <c r="G53" s="30">
         <v>4</v>
       </c>
-      <c r="H53" s="35">
+      <c r="H53" s="30">
         <v>2</v>
       </c>
-      <c r="I53" s="38"/>
-      <c r="L53" s="45">
+      <c r="I53" s="33"/>
+      <c r="L53" s="40">
         <f>C53-2</f>
         <v>2</v>
       </c>
-      <c r="M53" s="29">
+      <c r="M53" s="24">
         <f t="shared" si="28"/>
         <v>2</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="29">
         <f>E53-2</f>
         <v>2</v>
       </c>
-      <c r="O53" s="34">
+      <c r="O53" s="29">
         <f t="shared" si="29"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="P53" s="35">
+      <c r="P53" s="30">
         <f>G53-2</f>
         <v>2</v>
       </c>
-      <c r="Q53" s="35">
+      <c r="Q53" s="30">
         <f t="shared" si="30"/>
         <v>2</v>
       </c>
@@ -6845,68 +6886,68 @@
     </row>
     <row r="54" spans="1:24" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="43"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="38"/>
       <c r="I54" t="s">
         <v>104</v>
       </c>
-      <c r="L54" s="60">
+      <c r="L54" s="55">
         <f>AVERAGE(L5:M8,L10:M13,L15:M18,L20:M23,L25:M28,L30:M33,L35:M38,L40:M43,L45:M48,L50:M53)/2</f>
         <v>0.87924999999999931</v>
       </c>
-      <c r="M54" s="44"/>
-      <c r="N54" s="60">
+      <c r="M54" s="39"/>
+      <c r="N54" s="55">
         <f>AVERAGE(N5:O8,N10:O13,N15:O18,N20:O23,N25:O28,N30:O33,N35:O38,N40:O43,N45:O48,N50:O53)/2</f>
         <v>0.82037499999999974</v>
       </c>
-      <c r="O54" s="60"/>
-      <c r="P54" s="60">
+      <c r="O54" s="55"/>
+      <c r="P54" s="55">
         <f>AVERAGE(P5:Q8,P10:Q13,P15:Q18,P20:Q23,P25:Q28,P30:Q33,P35:Q38,P40:Q43,P45:Q48,P50:Q53)/2</f>
         <v>0.46874999999999972</v>
       </c>
-      <c r="Q54" s="44"/>
+      <c r="Q54" s="39"/>
     </row>
     <row r="55" spans="1:24" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="42" t="s">
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="J55" s="110"/>
-      <c r="K55" s="110"/>
-      <c r="L55" s="61">
+      <c r="J55" s="105"/>
+      <c r="K55" s="105"/>
+      <c r="L55" s="56">
         <f t="shared" ref="L55:Q55" si="31">AVERAGE(L5:L53)/2</f>
         <v>0.67637499999999973</v>
       </c>
-      <c r="M55" s="62">
+      <c r="M55" s="57">
         <f t="shared" si="31"/>
         <v>1.082125</v>
       </c>
-      <c r="N55" s="63">
+      <c r="N55" s="58">
         <f t="shared" si="31"/>
         <v>0.63162499999999999</v>
       </c>
-      <c r="O55" s="63">
+      <c r="O55" s="58">
         <f t="shared" si="31"/>
         <v>1.0091249999999996</v>
       </c>
-      <c r="P55" s="64">
+      <c r="P55" s="59">
         <f t="shared" si="31"/>
         <v>0.3862500000000002</v>
       </c>
-      <c r="Q55" s="65">
+      <c r="Q55" s="60">
         <f t="shared" si="31"/>
         <v>0.5512499999999998</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="35" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="31">
+      <c r="C56" s="26">
         <f>AVERAGE(C5:D8,C10:D13,C15:D18,C20:D23,C25:D28,C30:D33,C35:D38,C40:D43,C45:D48,C50:D53)</f>
         <v>2.9821250000000008</v>
       </c>
@@ -6918,484 +6959,555 @@
         <f>AVERAGE(G5:H8,G10:H13,G15:H18,G20:H23,G25:H28,G30:H33,G35:H38,G40:H43,G45:H48,G50:H53)</f>
         <v>2.4512499999999999</v>
       </c>
-      <c r="H56" s="47" t="s">
+      <c r="H56" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="I56" s="48" t="s">
+      <c r="I56" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="105">
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="100">
         <f>AVERAGE(L5,L10,L15,L20,L25,L30,L35,L40,L45,L50)/3.36</f>
         <v>0.43779761904761905</v>
       </c>
-      <c r="M56" s="106">
+      <c r="M56" s="101">
         <f>AVERAGE(M5,M10,M15,M20,M25,M30,M35,M40,M45,M50)/4</f>
         <v>0.75600000000000012</v>
       </c>
-      <c r="N56" s="53">
+      <c r="N56" s="48">
         <f>AVERAGE(N5,N10,N15,N20,N25,N30,N35,N40,N45,N50)/3.36</f>
         <v>0.35416666666666669</v>
       </c>
-      <c r="O56" s="100">
+      <c r="O56" s="95">
         <f>AVERAGE(O5,O10,O15,O20,O25,O30,O35,O40,O45,O50)/4</f>
         <v>0.65499999999999992</v>
       </c>
-      <c r="P56" s="107">
+      <c r="P56" s="102">
         <f>AVERAGE(P5,P10,P15,P20,P25,P30,P35,P40,P45,P50)/3.36</f>
         <v>0.29166666666666663</v>
       </c>
-      <c r="Q56" s="108">
+      <c r="Q56" s="103">
         <f>AVERAGE(Q5,Q10,Q15,Q20,Q25,Q30,Q35,Q40,Q45,Q50)/4</f>
         <v>0.3874999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="51" x14ac:dyDescent="0.2">
-      <c r="H57" s="49" t="s">
+      <c r="H57" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="I57" s="50" t="s">
+      <c r="I57" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="J57" s="26"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="54">
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="49">
         <f t="shared" ref="L57:Q57" si="32">AVERAGE(L6,L11,L16,L21,L26,L31,L36,L41,L46,L51)/3.33</f>
         <v>0.39399399399399399</v>
       </c>
-      <c r="M57" s="54">
+      <c r="M57" s="49">
         <f t="shared" si="32"/>
         <v>0.66876876876876856</v>
       </c>
-      <c r="N57" s="55">
+      <c r="N57" s="50">
         <f t="shared" si="32"/>
         <v>0.3423423423423424</v>
       </c>
-      <c r="O57" s="55">
+      <c r="O57" s="50">
         <f t="shared" si="32"/>
         <v>0.57357357357357364</v>
       </c>
-      <c r="P57" s="102">
+      <c r="P57" s="97">
         <f t="shared" si="32"/>
         <v>0.30330330330330335</v>
       </c>
-      <c r="Q57" s="97">
+      <c r="Q57" s="92">
         <f t="shared" si="32"/>
         <v>0.40240240240240233</v>
       </c>
     </row>
     <row r="58" spans="1:24" ht="51" x14ac:dyDescent="0.2">
-      <c r="F58" s="115" t="s">
+      <c r="F58" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="G58" s="116"/>
-      <c r="H58" s="49" t="s">
+      <c r="G58" s="164"/>
+      <c r="H58" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I58" s="50" t="s">
+      <c r="I58" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="54">
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="49">
         <f>AVERAGE(L7,L12,L17,L22,L27,L32,L37,L42,L47,L52)/4</f>
         <v>0.36075000000000002</v>
       </c>
-      <c r="M58" s="99">
+      <c r="M58" s="94">
         <f>AVERAGE(M7,M12,M17,M22,M27,M32,M37,M42,M47,M52)/3.33</f>
         <v>0.61831831831831818</v>
       </c>
-      <c r="N58" s="103">
+      <c r="N58" s="98">
         <f>AVERAGE(N7,N12,N17,N22,N27,N32,N37,N42,N47,N52)/4</f>
         <v>0.28749999999999992</v>
       </c>
-      <c r="O58" s="104">
+      <c r="O58" s="99">
         <f>AVERAGE(O7,O12,O17,O22,O27,O32,O37,O42,O47,O52)/3.33</f>
         <v>0.51951951951951947</v>
       </c>
-      <c r="P58" s="57">
+      <c r="P58" s="52">
         <f>AVERAGE(P7,P12,P17,P22,P27,P32,P37,P42,P47,P52)/4</f>
         <v>0.15</v>
       </c>
-      <c r="Q58" s="56">
+      <c r="Q58" s="51">
         <f>AVERAGE(Q7,Q12,Q17,Q22,Q27,Q32,Q37,Q42,Q47,Q52)/3.33</f>
         <v>0.28828828828828829</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="52" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H59" s="51" t="s">
+      <c r="H59" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="I59" s="52" t="s">
+      <c r="I59" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="58">
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="53">
         <f>AVERAGE(L8,L13,L18,L23,L28,L33,L38,L43,L48,L53)/4</f>
         <v>0.29625000000000001</v>
       </c>
-      <c r="M59" s="58">
+      <c r="M59" s="53">
         <f>AVERAGE(M8,M13,M18,M23,M28,M33,M38,M43,M48,M53)/4</f>
         <v>0.33674999999999999</v>
       </c>
-      <c r="N59" s="59">
+      <c r="N59" s="54">
         <f>AVERAGE(N8,N13,N18,N23,N28,N33,N38,N43,N48,N53)/4</f>
         <v>0.39324999999999999</v>
       </c>
-      <c r="O59" s="59">
+      <c r="O59" s="54">
         <f>AVERAGE(O8,O13,O18,O23,O28,O33,O38,O43,O48,O53)/4</f>
         <v>0.45324999999999999</v>
       </c>
-      <c r="P59" s="101">
+      <c r="P59" s="96">
         <f>AVERAGE(P8,P13,P18,P23,P28,P33,P38,P43,P48,P53)/4</f>
         <v>0.125</v>
       </c>
-      <c r="Q59" s="101">
+      <c r="Q59" s="96">
         <f>AVERAGE(Q8,Q13,Q18,Q23,Q28,Q33,Q38,Q43,Q48,Q53)/4</f>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="20" thickTop="1" x14ac:dyDescent="0.2">
       <c r="H60" s="1"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="26"/>
-      <c r="M60" s="66"/>
-      <c r="N60" s="67"/>
-      <c r="O60" s="66"/>
-      <c r="P60" s="66"/>
-      <c r="Q60" s="66"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="M60" s="61"/>
+      <c r="N60" s="62"/>
+      <c r="O60" s="61"/>
+      <c r="P60" s="61"/>
+      <c r="Q60" s="61"/>
     </row>
     <row r="61" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L61" s="68" t="s">
+      <c r="L61" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="M61" s="68" t="s">
+      <c r="M61" s="63" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:24" ht="35" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="H62" s="47" t="s">
+      <c r="H62" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="I62" s="39" t="s">
+      <c r="I62" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="L62" s="78">
+      <c r="L62" s="73">
         <f>AVERAGE(L56,N56,P56)</f>
         <v>0.3612103174603174</v>
       </c>
-      <c r="M62" s="78">
+      <c r="M62" s="73">
         <f>AVERAGE(M56,O56,Q56)</f>
         <v>0.59950000000000003</v>
       </c>
     </row>
     <row r="63" spans="1:24" ht="51" x14ac:dyDescent="0.2">
-      <c r="H63" s="49" t="s">
+      <c r="H63" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="I63" s="40" t="s">
+      <c r="I63" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="L63" s="78">
+      <c r="L63" s="73">
         <f t="shared" ref="L63:M64" si="33">AVERAGE(L57,N57,P57)</f>
         <v>0.34654654654654654</v>
       </c>
-      <c r="M63" s="78">
+      <c r="M63" s="73">
         <f t="shared" si="33"/>
         <v>0.54824824824824825</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="52" x14ac:dyDescent="0.25">
-      <c r="F64" s="111" t="s">
+      <c r="F64" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="G64" s="112"/>
-      <c r="H64" s="49" t="s">
+      <c r="G64" s="163"/>
+      <c r="H64" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I64" s="40" t="s">
+      <c r="I64" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="L64" s="78">
+      <c r="L64" s="73">
         <f t="shared" si="33"/>
         <v>0.26608333333333334</v>
       </c>
-      <c r="M64" s="78">
+      <c r="M64" s="73">
         <f t="shared" si="33"/>
         <v>0.47537537537537528</v>
       </c>
     </row>
     <row r="65" spans="6:17" ht="52" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F65" s="98"/>
-      <c r="G65" s="98"/>
-      <c r="H65" s="51" t="s">
+      <c r="F65" s="93"/>
+      <c r="G65" s="93"/>
+      <c r="H65" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="I65" s="41" t="s">
+      <c r="I65" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="L65" s="78">
+      <c r="L65" s="73">
         <f>AVERAGE(L59,N59,P59)</f>
         <v>0.27150000000000002</v>
       </c>
-      <c r="M65" s="79" t="s">
+      <c r="M65" s="74" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="66" spans="6:17" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="F66" s="98"/>
-      <c r="G66" s="98"/>
+      <c r="F66" s="93"/>
+      <c r="G66" s="93"/>
       <c r="H66" s="1"/>
-      <c r="L66" s="70"/>
-      <c r="M66" s="71"/>
+      <c r="L66" s="65"/>
+      <c r="M66" s="66"/>
     </row>
     <row r="67" spans="6:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F67" s="98"/>
-      <c r="G67" s="98"/>
-      <c r="L67" s="68" t="s">
+      <c r="F67" s="93"/>
+      <c r="G67" s="93"/>
+      <c r="L67" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="M67" s="68" t="s">
+      <c r="M67" s="63" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="68" spans="6:17" ht="35" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="F68" s="98"/>
-      <c r="G68" s="98"/>
-      <c r="H68" s="47" t="s">
+      <c r="F68" s="93"/>
+      <c r="G68" s="93"/>
+      <c r="H68" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="I68" s="72" t="s">
+      <c r="I68" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="J68" s="69"/>
-      <c r="K68" s="69"/>
-      <c r="L68" s="78">
+      <c r="J68" s="64"/>
+      <c r="K68" s="64"/>
+      <c r="L68" s="73">
         <f>AVERAGE(L56:Q56)</f>
         <v>0.48035515873015866</v>
       </c>
-      <c r="M68" s="78">
+      <c r="M68" s="73">
         <f>MEDIAN(L56:Q56)</f>
         <v>0.41264880952380945</v>
       </c>
     </row>
     <row r="69" spans="6:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="F69" s="98"/>
-      <c r="G69" s="98"/>
-      <c r="H69" s="49" t="s">
+      <c r="F69" s="93"/>
+      <c r="G69" s="93"/>
+      <c r="H69" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="I69" s="73" t="s">
+      <c r="I69" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="J69" s="69"/>
-      <c r="K69" s="69"/>
-      <c r="L69" s="78">
+      <c r="J69" s="64"/>
+      <c r="K69" s="64"/>
+      <c r="L69" s="73">
         <f t="shared" ref="L69:L71" si="34">AVERAGE(L57:Q57)</f>
         <v>0.44739739739739742</v>
       </c>
-      <c r="M69" s="78">
+      <c r="M69" s="73">
         <f>MEDIAN(L57:Q57)</f>
         <v>0.39819819819819813</v>
       </c>
     </row>
     <row r="70" spans="6:17" ht="52" x14ac:dyDescent="0.25">
-      <c r="F70" s="111" t="s">
+      <c r="F70" s="162" t="s">
         <v>119</v>
       </c>
-      <c r="G70" s="112"/>
-      <c r="H70" s="49" t="s">
+      <c r="G70" s="163"/>
+      <c r="H70" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I70" s="73" t="s">
+      <c r="I70" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="J70" s="69"/>
-      <c r="K70" s="69"/>
-      <c r="L70" s="78">
+      <c r="J70" s="64"/>
+      <c r="K70" s="64"/>
+      <c r="L70" s="73">
         <f t="shared" si="34"/>
         <v>0.37072935435435433</v>
       </c>
-      <c r="M70" s="78">
+      <c r="M70" s="73">
         <f>MEDIAN(L58:Q58)</f>
         <v>0.32451914414414418</v>
       </c>
     </row>
     <row r="71" spans="6:17" ht="52" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F71" s="98"/>
-      <c r="G71" s="98"/>
-      <c r="H71" s="51" t="s">
+      <c r="F71" s="93"/>
+      <c r="G71" s="93"/>
+      <c r="H71" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="I71" s="74" t="s">
+      <c r="I71" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="J71" s="69"/>
-      <c r="K71" s="69"/>
-      <c r="L71" s="78">
+      <c r="J71" s="64"/>
+      <c r="K71" s="64"/>
+      <c r="L71" s="73">
         <f t="shared" si="34"/>
         <v>0.29075000000000001</v>
       </c>
-      <c r="M71" s="79" t="s">
+      <c r="M71" s="74" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="72" spans="6:17" ht="20" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="F72" s="98"/>
-      <c r="G72" s="98"/>
+      <c r="F72" s="93"/>
+      <c r="G72" s="93"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="69"/>
-      <c r="K72" s="69"/>
-      <c r="L72" s="80"/>
-      <c r="M72" s="81"/>
+      <c r="I72" s="64"/>
+      <c r="J72" s="64"/>
+      <c r="K72" s="64"/>
+      <c r="L72" s="75"/>
+      <c r="M72" s="76"/>
     </row>
     <row r="73" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="F73" s="98"/>
-      <c r="G73" s="98"/>
+      <c r="F73" s="93"/>
+      <c r="G73" s="93"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="69"/>
-      <c r="J73" s="69"/>
-      <c r="K73" s="69"/>
-      <c r="L73" s="117" t="s">
+      <c r="I73" s="64"/>
+      <c r="J73" s="64"/>
+      <c r="K73" s="64"/>
+      <c r="L73" s="165" t="s">
         <v>37</v>
       </c>
-      <c r="M73" s="117"/>
-      <c r="N73" s="118" t="s">
+      <c r="M73" s="165"/>
+      <c r="N73" s="166" t="s">
         <v>32</v>
       </c>
-      <c r="O73" s="118"/>
-      <c r="P73" s="119" t="s">
+      <c r="O73" s="166"/>
+      <c r="P73" s="167" t="s">
         <v>33</v>
       </c>
-      <c r="Q73" s="119"/>
+      <c r="Q73" s="167"/>
     </row>
     <row r="74" spans="6:17" ht="22" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F74" s="98"/>
-      <c r="G74" s="98"/>
-      <c r="L74" s="96" t="s">
+      <c r="F74" s="93"/>
+      <c r="G74" s="93"/>
+      <c r="L74" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="M74" s="96" t="s">
+      <c r="M74" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="N74" s="96" t="s">
+      <c r="N74" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="O74" s="96" t="s">
+      <c r="O74" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="P74" s="96" t="s">
+      <c r="P74" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="Q74" s="96" t="s">
+      <c r="Q74" s="91" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="75" spans="6:17" ht="35" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="F75" s="98"/>
-      <c r="G75" s="98"/>
-      <c r="H75" s="47" t="s">
+      <c r="F75" s="93"/>
+      <c r="G75" s="93"/>
+      <c r="H75" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="I75" s="75" t="s">
+      <c r="I75" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="85"/>
-      <c r="M75" s="82" t="s">
+      <c r="J75" s="21"/>
+      <c r="K75" s="21"/>
+      <c r="L75" s="80"/>
+      <c r="M75" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="N75" s="90"/>
-      <c r="O75" s="87" t="s">
+      <c r="N75" s="85"/>
+      <c r="O75" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="P75" s="94"/>
-      <c r="Q75" s="92" t="s">
+      <c r="P75" s="89"/>
+      <c r="Q75" s="87" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="76" spans="6:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="F76" s="98"/>
-      <c r="G76" s="98"/>
-      <c r="H76" s="49" t="s">
+      <c r="F76" s="93"/>
+      <c r="G76" s="93"/>
+      <c r="H76" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="I76" s="76" t="s">
+      <c r="I76" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="109" t="s">
+      <c r="J76" s="21"/>
+      <c r="K76" s="21"/>
+      <c r="L76" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="M76" s="83"/>
-      <c r="N76" s="90"/>
-      <c r="O76" s="88"/>
-      <c r="P76" s="95"/>
-      <c r="Q76" s="92" t="s">
+      <c r="M76" s="78"/>
+      <c r="N76" s="85"/>
+      <c r="O76" s="83"/>
+      <c r="P76" s="90"/>
+      <c r="Q76" s="87" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="77" spans="6:17" ht="52" x14ac:dyDescent="0.25">
-      <c r="F77" s="111" t="s">
+      <c r="F77" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="G77" s="112"/>
-      <c r="H77" s="49" t="s">
+      <c r="G77" s="163"/>
+      <c r="H77" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I77" s="76" t="s">
+      <c r="I77" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="85" t="s">
+      <c r="J77" s="21"/>
+      <c r="K77" s="21"/>
+      <c r="L77" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="M77" s="83"/>
-      <c r="N77" s="90"/>
-      <c r="O77" s="88"/>
-      <c r="P77" s="94" t="s">
+      <c r="M77" s="78"/>
+      <c r="N77" s="85"/>
+      <c r="O77" s="83"/>
+      <c r="P77" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="Q77" s="92" t="s">
+      <c r="Q77" s="87" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="78" spans="6:17" ht="52" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H78" s="51" t="s">
+      <c r="H78" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="I78" s="77" t="s">
+      <c r="I78" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="86"/>
-      <c r="M78" s="84" t="s">
+      <c r="J78" s="21"/>
+      <c r="K78" s="21"/>
+      <c r="L78" s="81"/>
+      <c r="M78" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="N78" s="91" t="s">
+      <c r="N78" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="O78" s="89" t="s">
+      <c r="O78" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="P78" s="94" t="s">
+      <c r="P78" s="89" t="s">
         <v>112</v>
       </c>
-      <c r="Q78" s="93" t="s">
+      <c r="Q78" s="88" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="6:17" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="87">
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="L9:M9"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:B3"/>
@@ -7412,77 +7524,6 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="N49:O49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7534,269 +7575,268 @@
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="37.5" style="14" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" style="199" customWidth="1"/>
+    <col min="3" max="3" width="37.5" style="12" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="135" customWidth="1"/>
     <col min="6" max="6" width="11.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" style="21" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="61" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:9" s="194" customFormat="1" ht="61" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="191" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="140" t="s">
+      <c r="C1" s="192" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="141" t="s">
+      <c r="D1" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="197" t="s">
+      <c r="E1" s="195" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="22" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="61" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="175">
+      <c r="A2" s="168">
         <v>1</v>
       </c>
-      <c r="B2" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="144" t="s">
+      <c r="B2" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="190"/>
-      <c r="E2" s="198">
+      <c r="D2" s="127"/>
+      <c r="E2" s="134">
         <f>IF(D2="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="181">
+      <c r="F2" s="171">
         <f>IF(SUM(E2:E4)=0,0,IF(SUM(E2:E4)=1,1,IF(SUM(E2:E4)=2,2,IF(SUM(E2:E4)=3,3,IF(SUM(E2:E4)=4,4)))))</f>
         <v>0</v>
       </c>
-      <c r="G2" s="182"/>
-      <c r="H2" s="26" t="str">
+      <c r="G2" s="124"/>
+      <c r="H2" s="21" t="str">
         <f t="shared" ref="H2:H33" si="0">IF(E2=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="175"/>
-      <c r="B3" s="148"/>
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="168"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="191"/>
-      <c r="E3" s="199">
+      <c r="D3" s="128"/>
+      <c r="E3" s="135">
         <f>IF(D3="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="180"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="26" t="str">
+      <c r="F3" s="143"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="52" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="175"/>
-      <c r="B4" s="148"/>
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="168"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="199">
+      <c r="D4" s="129"/>
+      <c r="E4" s="135">
         <f>IF(D4="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="180"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="26" t="str">
+      <c r="F4" s="143"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="175"/>
-      <c r="B5" s="143" t="s">
+      <c r="A5" s="168"/>
+      <c r="B5" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="190"/>
-      <c r="E5" s="198">
+      <c r="D5" s="127"/>
+      <c r="E5" s="134">
         <f>IF(D5="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="188">
+      <c r="F5" s="173">
         <f>IF(SUM(E5:E7)=0,0,IF(SUM(E5:E7)=1,1,IF(SUM(E5:E7)&lt;=3,2,IF(SUM(E5:E7)&lt;=5,3,IF(SUM(E5:E7)=6,4)))))</f>
         <v>0</v>
       </c>
-      <c r="G5" s="182"/>
-      <c r="H5" s="26" t="str">
+      <c r="G5" s="124"/>
+      <c r="H5" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="175"/>
-      <c r="B6" s="148"/>
-      <c r="C6" s="18" t="s">
+      <c r="A6" s="168"/>
+      <c r="B6" s="170"/>
+      <c r="C6" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="191"/>
-      <c r="E6" s="200">
+      <c r="D6" s="128"/>
+      <c r="E6" s="136">
         <f>IF(D6="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="186"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="26" t="str">
+      <c r="F6" s="174"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="175"/>
-      <c r="B7" s="149"/>
-      <c r="C7" s="150" t="s">
+      <c r="A7" s="168"/>
+      <c r="B7" s="172"/>
+      <c r="C7" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="193"/>
-      <c r="E7" s="201">
+      <c r="D7" s="130"/>
+      <c r="E7" s="137">
         <f>IF(D7="+", 3,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="189"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="26" t="str">
+      <c r="F7" s="175"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="21" t="str">
         <f>IF(E7=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="175"/>
-      <c r="B8" s="143" t="s">
+      <c r="A8" s="168"/>
+      <c r="B8" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="106" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="190"/>
-      <c r="E8" s="198">
+      <c r="D8" s="127"/>
+      <c r="E8" s="134">
         <f>IF(D8="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="181">
+      <c r="F8" s="171">
         <f>IF(SUM(E8:E12)=0,0,IF(SUM(E8:E12)&lt;=2,1,IF(SUM(E8:E12)&lt;=4,2,IF(SUM(E8:E12)&lt;=6,3,IF(SUM(E8:E12)=7,4)))))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="182"/>
-      <c r="H8" s="26" t="str">
+      <c r="G8" s="124"/>
+      <c r="H8" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="175"/>
-      <c r="B9" s="148"/>
-      <c r="C9" s="18" t="s">
+      <c r="A9" s="168"/>
+      <c r="B9" s="170"/>
+      <c r="C9" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="191"/>
-      <c r="E9" s="200">
+      <c r="D9" s="128"/>
+      <c r="E9" s="136">
         <f>IF(D9="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="180"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="26" t="str">
+      <c r="F9" s="143"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="21" t="str">
         <f>IF(E9=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="109" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="175"/>
-      <c r="B10" s="148"/>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="168"/>
+      <c r="B10" s="170"/>
+      <c r="C10" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="191"/>
-      <c r="E10" s="200">
+      <c r="D10" s="128"/>
+      <c r="E10" s="136">
         <f>IF(D10="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="180"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="26" t="str">
+      <c r="F10" s="143"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="144" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="175"/>
-      <c r="B11" s="148"/>
-      <c r="C11" s="18" t="s">
+      <c r="A11" s="168"/>
+      <c r="B11" s="170"/>
+      <c r="C11" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="191"/>
-      <c r="E11" s="200">
+      <c r="D11" s="128"/>
+      <c r="E11" s="136">
         <f>IF(D11="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="180"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="26" t="str">
+      <c r="F11" s="143"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="175"/>
-      <c r="B12" s="149"/>
-      <c r="C12" s="150" t="s">
+      <c r="A12" s="168"/>
+      <c r="B12" s="172"/>
+      <c r="C12" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="193"/>
-      <c r="E12" s="201">
+      <c r="D12" s="130"/>
+      <c r="E12" s="137">
         <f>IF(D12="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="184"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="26" t="str">
+      <c r="F12" s="176"/>
+      <c r="G12" s="126"/>
+      <c r="H12" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="43" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="139">
+      <c r="A13" s="177">
         <v>2</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="142"/>
-      <c r="F13" s="187">
+      <c r="C13" s="14"/>
+      <c r="F13" s="10">
         <f>IF(AVERAGE(F2:F12)&lt;=0.8,0,IF(AVERAGE(F2:F12)&lt;=1.6,1,IF(AVERAGE(F2:F12)&lt;=2.4,2,IF(AVERAGE(F2:F12)&lt;=3.2,3,IF(AVERAGE(F2:F12)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -7810,56 +7850,55 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="139"/>
-      <c r="B14" s="163" t="s">
+      <c r="A14" s="177"/>
+      <c r="B14" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="106" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="190"/>
-      <c r="E14" s="198">
+      <c r="D14" s="127"/>
+      <c r="E14" s="134">
         <f>IF(D14="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="181">
+      <c r="F14" s="171">
         <f>IF(SUM(E14:E15)=0,0,IF(SUM(E14:E15)=2,2,IF(SUM(E14:E15)=4,4)))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="182"/>
-      <c r="H14" s="26" t="str">
+      <c r="G14" s="124"/>
+      <c r="H14" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="139"/>
-      <c r="B15" s="165"/>
-      <c r="C15" s="150" t="s">
+      <c r="A15" s="177"/>
+      <c r="B15" s="179"/>
+      <c r="C15" s="109" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="193"/>
-      <c r="E15" s="201">
+      <c r="D15" s="130"/>
+      <c r="E15" s="137">
         <f>IF(D15="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="184"/>
-      <c r="G15" s="185"/>
-      <c r="H15" s="26" t="str">
+      <c r="F15" s="176"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="175">
+      <c r="A16" s="168">
         <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="142"/>
-      <c r="F16" s="187">
+      <c r="C16" s="14"/>
+      <c r="F16" s="10">
         <f>IF(AVERAGE(F13:F15)&lt;=0.8,0,IF(AVERAGE(F13:F15)&lt;=1.6,1,IF(AVERAGE(F13:F15)&lt;=2.4,2,IF(AVERAGE(F13:F15)&lt;=3.2,3,IF(AVERAGE(F13:F15)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -7873,151 +7912,150 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="94" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="175"/>
-      <c r="B17" s="143" t="s">
+      <c r="A17" s="168"/>
+      <c r="B17" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="106" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="190"/>
-      <c r="E17" s="198">
+      <c r="D17" s="127"/>
+      <c r="E17" s="134">
         <f>IF(D17="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="181">
+      <c r="F17" s="171">
         <f>IF(SUM(E17:E20)=0,0,IF(SUM(E17:E20)=1,1,IF(SUM(E17:E20)&lt;=5,2,IF(SUM(E17:E20)&lt;=7,3,IF(SUM(E17:E20)&gt;=8,4)))))</f>
         <v>0</v>
       </c>
-      <c r="G17" s="182"/>
-      <c r="H17" s="26" t="str">
+      <c r="G17" s="124"/>
+      <c r="H17" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="103" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="175"/>
-      <c r="B18" s="148"/>
-      <c r="C18" s="18" t="s">
+      <c r="A18" s="168"/>
+      <c r="B18" s="170"/>
+      <c r="C18" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="191"/>
-      <c r="E18" s="200">
+      <c r="D18" s="128"/>
+      <c r="E18" s="136">
         <f>IF(D18="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="180"/>
-      <c r="G18" s="183"/>
-      <c r="H18" s="26" t="str">
+      <c r="F18" s="143"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="175"/>
-      <c r="B19" s="148"/>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="168"/>
+      <c r="B19" s="170"/>
+      <c r="C19" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="191"/>
-      <c r="E19" s="200">
+      <c r="D19" s="128"/>
+      <c r="E19" s="136">
         <f>IF(D19="+", 3,0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="180"/>
-      <c r="G19" s="183"/>
-      <c r="H19" s="26" t="str">
+      <c r="F19" s="143"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="175"/>
-      <c r="B20" s="149"/>
-      <c r="C20" s="150" t="s">
+      <c r="A20" s="168"/>
+      <c r="B20" s="172"/>
+      <c r="C20" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="193"/>
-      <c r="E20" s="201">
+      <c r="D20" s="130"/>
+      <c r="E20" s="137">
         <f>IF(D20="+", 4,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="184"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="26" t="str">
+      <c r="F20" s="176"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="175"/>
-      <c r="B21" s="143" t="s">
+      <c r="A21" s="168"/>
+      <c r="B21" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="169" t="s">
+      <c r="C21" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="194"/>
-      <c r="E21" s="198">
+      <c r="D21" s="131"/>
+      <c r="E21" s="134">
         <f>IF(D21="+", 0,0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="181">
+      <c r="F21" s="171">
         <f>IF(SUM(E21:E23)=0,0,IF(SUM(E21:E23)=1,2,IF(SUM(E21:E23)=2,4)))</f>
         <v>0</v>
       </c>
-      <c r="G21" s="182"/>
-      <c r="H21" s="26" t="str">
+      <c r="G21" s="124"/>
+      <c r="H21" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="175"/>
-      <c r="B22" s="148"/>
-      <c r="C22" s="22" t="s">
+      <c r="A22" s="168"/>
+      <c r="B22" s="170"/>
+      <c r="C22" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="195"/>
-      <c r="E22" s="199">
+      <c r="D22" s="132"/>
+      <c r="E22" s="135">
         <f>IF(D22="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="180"/>
-      <c r="G22" s="183"/>
-      <c r="H22" s="26" t="str">
+      <c r="F22" s="143"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="65" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="175"/>
-      <c r="B23" s="149"/>
-      <c r="C23" s="172" t="s">
+      <c r="A23" s="168"/>
+      <c r="B23" s="172"/>
+      <c r="C23" s="119" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="196"/>
-      <c r="E23" s="202">
+      <c r="D23" s="133"/>
+      <c r="E23" s="138">
         <f>IF(D23="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="184"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="26" t="str">
+      <c r="F23" s="176"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="175">
+      <c r="A24" s="168">
         <v>4</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="142"/>
-      <c r="F24" s="187">
+      <c r="C24" s="14"/>
+      <c r="F24" s="10">
         <f>IF(AVERAGE(F16:F23)&lt;=0.8,0,IF(AVERAGE(F16:F23)&lt;=1.6,1,IF(AVERAGE(F16:F23)&lt;=2.4,2,IF(AVERAGE(F16:F23)&lt;=3.2,3,IF(AVERAGE(F16:F23)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -8031,173 +8069,173 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="175"/>
-      <c r="B25" s="143" t="s">
+      <c r="A25" s="168"/>
+      <c r="B25" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="169" t="s">
+      <c r="C25" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="194"/>
-      <c r="E25" s="198">
+      <c r="D25" s="131"/>
+      <c r="E25" s="134">
         <f>IF(D25="+", 0,0)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="181">
+      <c r="F25" s="171">
         <f>IF(SUM(E25:E28)=0,0,IF(SUM(E25:E28)=1,1,IF(SUM(E25:E28)=2,3,IF(SUM(E25:E28)=3,4))))</f>
         <v>0</v>
       </c>
-      <c r="G25" s="182"/>
-      <c r="H25" s="26" t="str">
+      <c r="G25" s="124"/>
+      <c r="H25" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="175"/>
-      <c r="B26" s="148"/>
-      <c r="C26" s="22" t="s">
+      <c r="A26" s="168"/>
+      <c r="B26" s="170"/>
+      <c r="C26" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="195"/>
-      <c r="E26" s="199">
+      <c r="D26" s="132"/>
+      <c r="E26" s="135">
         <f>IF(D26="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="180"/>
-      <c r="G26" s="183"/>
-      <c r="H26" s="26" t="str">
+      <c r="F26" s="143"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="175"/>
-      <c r="B27" s="148"/>
-      <c r="C27" s="22" t="s">
+      <c r="A27" s="168"/>
+      <c r="B27" s="170"/>
+      <c r="C27" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D27" s="195"/>
-      <c r="E27" s="199">
+      <c r="D27" s="132"/>
+      <c r="E27" s="135">
         <f>IF(D27="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="180"/>
-      <c r="G27" s="183"/>
-      <c r="H27" s="26" t="str">
+      <c r="F27" s="143"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="175"/>
-      <c r="B28" s="149"/>
-      <c r="C28" s="172" t="s">
+      <c r="A28" s="168"/>
+      <c r="B28" s="172"/>
+      <c r="C28" s="119" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="196"/>
-      <c r="E28" s="202">
+      <c r="D28" s="133"/>
+      <c r="E28" s="138">
         <f>IF(D28="+", 3,0)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="184"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="26" t="str">
+      <c r="F28" s="176"/>
+      <c r="G28" s="126"/>
+      <c r="H28" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="175"/>
-      <c r="B29" s="143" t="s">
+      <c r="A29" s="168"/>
+      <c r="B29" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="169" t="s">
+      <c r="C29" s="116" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="194"/>
-      <c r="E29" s="198">
+      <c r="D29" s="131"/>
+      <c r="E29" s="134">
         <f>IF(D29="+", 0,0)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="181">
+      <c r="F29" s="171">
         <f>IF(SUM(E29:E33)=0,0,IF(SUM(E29:E33)=1,1,IF(SUM(E29:E33)=2,2,IF(SUM(E29:E33)=3,3,IF(SUM(E29:E33)&lt;=20,4)))))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="182"/>
-      <c r="H29" s="26" t="str">
+      <c r="G29" s="124"/>
+      <c r="H29" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="175"/>
-      <c r="B30" s="148"/>
-      <c r="C30" s="22" t="s">
+      <c r="A30" s="168"/>
+      <c r="B30" s="170"/>
+      <c r="C30" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="195"/>
-      <c r="E30" s="199">
+      <c r="D30" s="132"/>
+      <c r="E30" s="135">
         <f>IF(D30="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="180"/>
-      <c r="G30" s="183"/>
-      <c r="H30" s="26" t="str">
+      <c r="F30" s="143"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="175"/>
-      <c r="B31" s="148"/>
-      <c r="C31" s="22" t="s">
+      <c r="A31" s="168"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D31" s="195"/>
-      <c r="E31" s="199">
+      <c r="D31" s="132"/>
+      <c r="E31" s="135">
         <f>IF(D31="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="180"/>
-      <c r="G31" s="183"/>
-      <c r="H31" s="26" t="str">
+      <c r="F31" s="143"/>
+      <c r="G31" s="125"/>
+      <c r="H31" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="175"/>
-      <c r="B32" s="148"/>
-      <c r="C32" s="22" t="s">
+      <c r="A32" s="168"/>
+      <c r="B32" s="170"/>
+      <c r="C32" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D32" s="195"/>
-      <c r="E32" s="199">
+      <c r="D32" s="132"/>
+      <c r="E32" s="135">
         <f>IF(D32="+", 3,0)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="180"/>
-      <c r="G32" s="183"/>
-      <c r="H32" s="26" t="str">
+      <c r="F32" s="143"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="175"/>
-      <c r="B33" s="149"/>
-      <c r="C33" s="172" t="s">
+      <c r="A33" s="168"/>
+      <c r="B33" s="172"/>
+      <c r="C33" s="119" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="196"/>
-      <c r="E33" s="202">
+      <c r="D33" s="133"/>
+      <c r="E33" s="138">
         <f>IF(D33="+", 4,0)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="184"/>
-      <c r="G33" s="185"/>
-      <c r="H33" s="26" t="str">
+      <c r="F33" s="176"/>
+      <c r="G33" s="126"/>
+      <c r="H33" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
@@ -8217,13 +8255,13 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="16"/>
+      <c r="A36" s="197"/>
       <c r="B36" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="17"/>
+      <c r="A37" s="204"/>
       <c r="B37" t="s">
         <v>129</v>
       </c>
@@ -8236,13 +8274,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="F8:F12"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="F29:F33"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="F14:F15"/>
@@ -8251,34 +8287,21 @@
     <mergeCell ref="F17:F20"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="F8:F12"/>
   </mergeCells>
   <conditionalFormatting sqref="E2:E33">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H1048576">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I1048576">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8293,44 +8316,44 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="37.5" style="14" customWidth="1"/>
-    <col min="4" max="4" width="5.5" customWidth="1"/>
-    <col min="5" max="5" width="31" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="37.5" style="12" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="31" style="13" customWidth="1"/>
     <col min="6" max="6" width="11.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" style="6" customWidth="1"/>
     <col min="8" max="8" width="21.1640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="22.33203125" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="21" customWidth="1"/>
+    <col min="11" max="11" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="26" customFormat="1" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" s="196" customFormat="1" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="191" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="140" t="s">
+      <c r="C1" s="192" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="141" t="s">
+      <c r="D1" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="195" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="191" t="s">
         <v>157</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="191" t="s">
         <v>158</v>
       </c>
       <c r="J1" s="9" t="s">
@@ -8341,273 +8364,273 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="58" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="175">
+      <c r="A2" s="168">
         <v>1</v>
       </c>
-      <c r="B2" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="146" t="s">
+      <c r="B2" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="106"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="147"/>
-      <c r="G2" s="177">
+      <c r="F2" s="187"/>
+      <c r="G2" s="122">
         <f>IF(F2="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="181">
+      <c r="H2" s="171">
         <f>IF(SUM(G2:G5)=0,0,IF(SUM(G2:G5)=1,1,IF(SUM(G2:G5)=2,2,IF(SUM(G2:G5)=3,3,IF(SUM(G2:G5)=4,4)))))</f>
         <v>0</v>
       </c>
-      <c r="I2" s="182"/>
-      <c r="J2" s="26" t="str">
+      <c r="I2" s="124"/>
+      <c r="J2" s="21" t="str">
         <f>IF(G2=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="61" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="175"/>
-      <c r="B3" s="148"/>
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="168"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="24"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="178">
+      <c r="G3" s="6">
         <f>IF(D3="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="180"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="26" t="str">
+      <c r="H3" s="143"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="21" t="str">
         <f t="shared" ref="J3:J40" si="0">IF(G3=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="175"/>
-      <c r="B4" s="148"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="25" t="s">
+      <c r="A4" s="168"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="178">
+      <c r="F4" s="188"/>
+      <c r="G4" s="6">
         <f>IF(F4="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="180"/>
-      <c r="I4" s="183"/>
-      <c r="J4" s="26" t="str">
+      <c r="H4" s="143"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="52" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="175"/>
-      <c r="B5" s="149"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="152" t="s">
+      <c r="A5" s="168"/>
+      <c r="B5" s="172"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="153"/>
-      <c r="G5" s="179">
+      <c r="F5" s="189"/>
+      <c r="G5" s="123">
         <f>IF(F5="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="184"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="26" t="str">
+      <c r="H5" s="176"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="175"/>
-      <c r="B6" s="143" t="s">
+      <c r="A6" s="168"/>
+      <c r="B6" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="144"/>
-      <c r="D6" s="154"/>
-      <c r="E6" s="155" t="s">
+      <c r="C6" s="106"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="156"/>
-      <c r="G6" s="177">
+      <c r="F6" s="190"/>
+      <c r="G6" s="122">
         <f>IF(F6="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="181">
+      <c r="H6" s="171">
         <f>IF(SUM(G6:G8)=0,0,IF(SUM(G6:G8)=1,1,IF(SUM(G6:G8)&lt;=3,2,IF(SUM(G6:G8)&lt;=5,3,IF(SUM(G6:G8)=6,4)))))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="182"/>
-      <c r="J6" s="26" t="str">
+      <c r="I6" s="124"/>
+      <c r="J6" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="175"/>
-      <c r="B7" s="148"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="25" t="s">
+      <c r="A7" s="168"/>
+      <c r="B7" s="170"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="178">
+      <c r="F7" s="188"/>
+      <c r="G7" s="6">
         <f>IF(G6=0, 0, IF(OR(F7="+"), 2,0))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="180"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="26" t="str">
+      <c r="H7" s="143"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="175"/>
-      <c r="B8" s="149"/>
-      <c r="C8" s="150" t="s">
+      <c r="A8" s="168"/>
+      <c r="B8" s="172"/>
+      <c r="C8" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="157"/>
-      <c r="E8" s="158"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="179">
+      <c r="D8" s="198"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="201"/>
+      <c r="G8" s="123">
         <f>IF(G6=0, 0, IF(OR(F8="+"), 3,0))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="184"/>
-      <c r="I8" s="185"/>
-      <c r="J8" s="26" t="str">
+      <c r="H8" s="176"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="21" t="str">
         <f>IF(G8=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="175"/>
-      <c r="B9" s="143" t="s">
+      <c r="A9" s="168"/>
+      <c r="B9" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="106" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="160"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="177">
+      <c r="D9" s="199"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="202"/>
+      <c r="G9" s="122">
         <f>IF(OR(F9="+",D9="+" ),2,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="181">
+      <c r="H9" s="171">
         <f>IF(SUM(G9:G13)=0,0,IF(SUM(G9:G13)&lt;=2,1,IF(SUM(G9:G13)&lt;=4,2,IF(SUM(G9:G13)&lt;=6,3,IF(SUM(G9:G13)=7,4)))))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="182"/>
-      <c r="J9" s="26" t="str">
+      <c r="I9" s="124"/>
+      <c r="J9" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="175"/>
-      <c r="B10" s="148"/>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="168"/>
+      <c r="B10" s="170"/>
+      <c r="C10" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="203">
+      <c r="D10" s="200"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="139">
         <f>IF(G9=0,0,IF(OR(F10="+",D10="+"),2,0))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="180"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="26" t="str">
+      <c r="H10" s="143"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="21" t="str">
         <f>IF(G10=0,"+","")</f>
         <v>+</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="109" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="175"/>
-      <c r="B11" s="148"/>
-      <c r="C11" s="18" t="s">
+      <c r="A11" s="168"/>
+      <c r="B11" s="170"/>
+      <c r="C11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="178">
+      <c r="D11" s="200"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="6">
         <f>IF(G10=0,0,IF(OR(F11="+",D11="+"),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="180"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="26" t="str">
+      <c r="H11" s="143"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="175"/>
-      <c r="B12" s="148"/>
-      <c r="C12" s="18" t="s">
+      <c r="A12" s="168"/>
+      <c r="B12" s="170"/>
+      <c r="C12" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="178">
+      <c r="D12" s="200"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="6">
         <f>IF(G10=0,0,IF(OR(F12="+",D12="+"),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="180"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="26" t="str">
+      <c r="H12" s="143"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="175"/>
-      <c r="B13" s="149"/>
-      <c r="C13" s="150" t="s">
+      <c r="A13" s="168"/>
+      <c r="B13" s="172"/>
+      <c r="C13" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="157"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="159"/>
-      <c r="G13" s="179">
+      <c r="D13" s="198"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="123">
         <f>IF(G10=0,0,IF(OR(F13="+",D13="+"),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="184"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="26" t="str">
+      <c r="H13" s="176"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="176">
+      <c r="A14" s="168">
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="24"/>
-      <c r="H14" s="187">
+      <c r="C14" s="14"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="19"/>
+      <c r="H14" s="10">
         <f>IF(AVERAGE(H2:H13)&lt;=0.8,0,IF(AVERAGE(H2:H13)&lt;=1.6,1,IF(AVERAGE(H2:H13)&lt;=2.4,2,IF(AVERAGE(H2:H13)&lt;=3.2,3,IF(AVERAGE(H2:H13)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -8615,192 +8638,192 @@
         <f>IF(H14=0,"не реализуется",IF(H14=1,"низкий",IF(H14=2,"средний",IF(H14=3,"выше среднего",IF(H14=4,"высокий")))))</f>
         <v>не реализуется</v>
       </c>
-      <c r="K14" s="1" t="str">
+      <c r="K14" s="4" t="str">
         <f>IF(H14&lt;4,"+","в рекомендациях не нуждается")</f>
         <v>+</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="176"/>
-      <c r="B15" s="163" t="s">
+      <c r="A15" s="168"/>
+      <c r="B15" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="144"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="155" t="s">
+      <c r="C15" s="106"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="156"/>
-      <c r="G15" s="177">
+      <c r="F15" s="190"/>
+      <c r="G15" s="122">
         <f>IF(F15="+", 0,0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="181">
+      <c r="H15" s="171">
         <f>IF(SUM(G15:G17)=0,0,IF(SUM(G15:G17)=1,2,IF(SUM(G15:G17)=2,4)))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="182"/>
-      <c r="J15" s="26" t="str">
+      <c r="I15" s="124"/>
+      <c r="J15" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="176"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="25" t="s">
+      <c r="A16" s="168"/>
+      <c r="B16" s="180"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="178">
+      <c r="F16" s="188"/>
+      <c r="G16" s="6">
         <f>IF(F16="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="180"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="26" t="str">
+      <c r="H16" s="143"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="176"/>
-      <c r="B17" s="165"/>
-      <c r="C17" s="150"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="152" t="s">
+      <c r="A17" s="168"/>
+      <c r="B17" s="179"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="153"/>
-      <c r="G17" s="179">
+      <c r="F17" s="189"/>
+      <c r="G17" s="123">
         <f>IF(F17="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="184"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="26" t="str">
+      <c r="H17" s="176"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="176"/>
-      <c r="B18" s="163" t="s">
+      <c r="A18" s="168"/>
+      <c r="B18" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="144" t="s">
+      <c r="C18" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="160"/>
-      <c r="E18" s="161"/>
-      <c r="F18" s="162"/>
-      <c r="G18" s="177">
+      <c r="D18" s="199"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="202"/>
+      <c r="G18" s="122">
         <f>IF(OR(F18="+",D18="+" ),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="181">
+      <c r="H18" s="171">
         <f>IF(SUM(G18:G22)=0,0,IF(SUM(G18:G22)=1,1,IF(SUM(G18:G22)=2,2,IF(SUM(G18:G22)&lt;4,3,IF(SUM(G18:G22)&lt;=5,4)))))</f>
         <v>0</v>
       </c>
-      <c r="I18" s="182"/>
-      <c r="J18" s="26" t="str">
+      <c r="I18" s="124"/>
+      <c r="J18" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="176"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="25" t="s">
+      <c r="A19" s="168"/>
+      <c r="B19" s="180"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="178">
+      <c r="F19" s="188"/>
+      <c r="G19" s="6">
         <f>IF(F19="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="180"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="26" t="str">
+      <c r="H19" s="143"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="176"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="18" t="s">
+      <c r="A20" s="168"/>
+      <c r="B20" s="180"/>
+      <c r="C20" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="178">
+      <c r="D20" s="200"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="6">
         <f>IF(OR(F20="+",D20="+" ),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="180"/>
-      <c r="I20" s="183"/>
-      <c r="J20" s="26" t="str">
+      <c r="H20" s="143"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="176"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="25" t="s">
+      <c r="A21" s="168"/>
+      <c r="B21" s="180"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="178">
+      <c r="F21" s="188"/>
+      <c r="G21" s="6">
         <f>IF(F21="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="180"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="26" t="str">
+      <c r="H21" s="143"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="176"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="150"/>
-      <c r="D22" s="151"/>
-      <c r="E22" s="158" t="s">
+      <c r="A22" s="168"/>
+      <c r="B22" s="179"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="153"/>
-      <c r="G22" s="179">
+      <c r="F22" s="189"/>
+      <c r="G22" s="123">
         <f>IF(F22="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="184"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="26" t="str">
+      <c r="H22" s="176"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="176">
+      <c r="A23" s="168">
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="24"/>
-      <c r="H23" s="187">
+      <c r="C23" s="14"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="19"/>
+      <c r="H23" s="10">
         <f>IF(AVERAGE(H14:H22)&lt;=0.8,0,IF(AVERAGE(H14:H22)&lt;=1.6,1,IF(AVERAGE(H14:H22)&lt;=2.4,2,IF(AVERAGE(H14:H22)&lt;=3.2,3,IF(AVERAGE(H14:H22)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -8808,172 +8831,172 @@
         <f>IF(H23=0,"не реализуется",IF(H23=1,"низкий",IF(H23=2,"средний",IF(H23=3,"выше среднего",IF(H23=4,"высокий")))))</f>
         <v>не реализуется</v>
       </c>
-      <c r="K23" s="1" t="str">
+      <c r="K23" s="4" t="str">
         <f>IF(H23&lt;4,"+","в рекомендациях не нуждается")</f>
         <v>+</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="94" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="176"/>
-      <c r="B24" s="204" t="s">
+      <c r="A24" s="168"/>
+      <c r="B24" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="160"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="162"/>
-      <c r="G24" s="177">
+      <c r="D24" s="199"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="202"/>
+      <c r="G24" s="122">
         <f>IF(OR(F24="+",D24="+" ),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="181">
+      <c r="H24" s="171">
         <f>IF(SUM(G24:G27)=0,0,IF(SUM(G24:G27)=1,1,IF(SUM(G24:G27)&lt;=5,2,IF(SUM(G24:G27)&lt;=7,3,IF(SUM(G24:G27)&lt;=10,4)))))</f>
         <v>0</v>
       </c>
-      <c r="I24" s="182"/>
-      <c r="J24" s="26" t="str">
+      <c r="I24" s="124"/>
+      <c r="J24" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="103" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="176"/>
-      <c r="B25" s="205"/>
-      <c r="C25" s="18" t="s">
+      <c r="A25" s="168"/>
+      <c r="B25" s="182"/>
+      <c r="C25" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="178">
+      <c r="D25" s="200"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="6">
         <f>IF(G24=0, 0, IF(OR(F25="+", D25="+"), 2, 0))</f>
         <v>0</v>
       </c>
-      <c r="H25" s="180"/>
-      <c r="I25" s="183"/>
-      <c r="J25" s="26" t="str">
+      <c r="H25" s="143"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="176"/>
-      <c r="B26" s="205"/>
-      <c r="C26" s="18" t="s">
+      <c r="A26" s="168"/>
+      <c r="B26" s="182"/>
+      <c r="C26" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="178">
+      <c r="D26" s="200"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="6">
         <f>IF(G24=0, 0, IF(OR(F26="+", D26="+"), 3, 0))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="180"/>
-      <c r="I26" s="183"/>
-      <c r="J26" s="26" t="str">
+      <c r="H26" s="143"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="176"/>
-      <c r="B27" s="206"/>
-      <c r="C27" s="150" t="s">
+      <c r="A27" s="168"/>
+      <c r="B27" s="183"/>
+      <c r="C27" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="157"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="179">
+      <c r="D27" s="198"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="201"/>
+      <c r="G27" s="123">
         <f>IF(G24=0, 0, IF(OR(F27="+", D27="+"), 4, 0))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="184"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="26" t="str">
+      <c r="H27" s="176"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="176"/>
-      <c r="B28" s="166" t="s">
+      <c r="A28" s="168"/>
+      <c r="B28" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="169" t="s">
+      <c r="C28" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="170"/>
-      <c r="E28" s="161"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="177">
+      <c r="D28" s="117"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="122">
         <f>IF(OR(F28="+",D28="+" ),0,0)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="181">
+      <c r="H28" s="171">
         <f>IF(SUM(G28:G30)=0,0,IF(SUM(G28:G30)=1,2,IF(SUM(G28:G30)=2,4)))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="182"/>
-      <c r="J28" s="26" t="str">
+      <c r="I28" s="124"/>
+      <c r="J28" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="176"/>
-      <c r="B29" s="167"/>
-      <c r="C29" s="22" t="s">
+      <c r="A29" s="168"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="178">
+      <c r="G29" s="6">
         <f>IF(D29="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="180"/>
-      <c r="I29" s="183"/>
-      <c r="J29" s="26" t="str">
+      <c r="H29" s="143"/>
+      <c r="I29" s="125"/>
+      <c r="J29" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="65" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="176"/>
-      <c r="B30" s="168"/>
-      <c r="C30" s="172" t="s">
+      <c r="A30" s="168"/>
+      <c r="B30" s="186"/>
+      <c r="C30" s="119" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="173"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="174"/>
-      <c r="G30" s="179">
+      <c r="D30" s="120"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="123">
         <f>IF(D30="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="184"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="26" t="str">
+      <c r="H30" s="176"/>
+      <c r="I30" s="126"/>
+      <c r="J30" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="176">
+      <c r="A31" s="168">
         <v>4</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="24"/>
-      <c r="H31" s="187">
+      <c r="C31" s="14"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="19"/>
+      <c r="H31" s="10">
         <f>IF(AVERAGE(H23:H30)&lt;=0.8,0,IF(AVERAGE(H23:H30)&lt;=1.6,1,IF(AVERAGE(H23:H30)&lt;=2.4,2,IF(AVERAGE(H23:H30)&lt;=3.2,3,IF(AVERAGE(H23:H30)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -8981,203 +9004,203 @@
         <f>IF(H31=0,"не реализуется",IF(H31=1,"низкий",IF(H31=2,"средний",IF(H31=3,"выше среднего",IF(H31=4,"высокий")))))</f>
         <v>не реализуется</v>
       </c>
-      <c r="K31" t="str">
+      <c r="K31" s="2" t="str">
         <f>IF(H31&lt;4,"+","в рекомендациях не нуждается")</f>
         <v>+</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="176"/>
-      <c r="B32" s="143" t="s">
+      <c r="A32" s="168"/>
+      <c r="B32" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="169" t="s">
+      <c r="C32" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="170"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="177">
+      <c r="D32" s="117"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="122">
         <f>IF(D32="+", 0,0)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="181">
+      <c r="H32" s="171">
         <f>IF(SUM(G32:G35)=0,0,IF(SUM(G32:G35)=1,1,IF(SUM(G32:G35)=2,3,IF(SUM(G32:G35)=3,4))))</f>
         <v>0</v>
       </c>
-      <c r="I32" s="182"/>
-      <c r="J32" s="26" t="str">
+      <c r="I32" s="124"/>
+      <c r="J32" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="176"/>
-      <c r="B33" s="148"/>
-      <c r="C33" s="22" t="s">
+      <c r="A33" s="168"/>
+      <c r="B33" s="170"/>
+      <c r="C33" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="24"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="178">
+      <c r="G33" s="6">
         <f>IF(D33="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H33" s="180"/>
-      <c r="I33" s="183"/>
-      <c r="J33" s="26" t="str">
+      <c r="H33" s="143"/>
+      <c r="I33" s="125"/>
+      <c r="J33" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="176"/>
-      <c r="B34" s="148"/>
-      <c r="C34" s="22" t="s">
+      <c r="A34" s="168"/>
+      <c r="B34" s="170"/>
+      <c r="C34" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="24"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="19"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="178">
+      <c r="G34" s="6">
         <f>IF(D34="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="180"/>
-      <c r="I34" s="183"/>
-      <c r="J34" s="26" t="str">
+      <c r="H34" s="143"/>
+      <c r="I34" s="125"/>
+      <c r="J34" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="176"/>
-      <c r="B35" s="149"/>
-      <c r="C35" s="172" t="s">
+      <c r="A35" s="168"/>
+      <c r="B35" s="172"/>
+      <c r="C35" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="173"/>
-      <c r="E35" s="158"/>
-      <c r="F35" s="174"/>
-      <c r="G35" s="179">
+      <c r="D35" s="120"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="123">
         <f>IF(D35="+", 3,0)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="184"/>
-      <c r="I35" s="185"/>
-      <c r="J35" s="26" t="str">
+      <c r="H35" s="176"/>
+      <c r="I35" s="126"/>
+      <c r="J35" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="176"/>
-      <c r="B36" s="143" t="s">
+      <c r="A36" s="168"/>
+      <c r="B36" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="169" t="s">
+      <c r="C36" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="170"/>
-      <c r="E36" s="161"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="177">
+      <c r="D36" s="117"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="122">
         <f>IF(D36="+", 0,0)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="181">
+      <c r="H36" s="171">
         <f>IF(SUM(G36:G40)=0,0,IF(SUM(G36:G40)=1,1,IF(SUM(G36:G40)=2,2,IF(SUM(G36:G40)=3,3,IF(SUM(G36:G40)=4,4)))))</f>
         <v>0</v>
       </c>
-      <c r="I36" s="182"/>
-      <c r="J36" s="26" t="str">
+      <c r="I36" s="124"/>
+      <c r="J36" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="176"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="22" t="s">
+      <c r="A37" s="168"/>
+      <c r="B37" s="170"/>
+      <c r="C37" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="23"/>
-      <c r="E37" s="24"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="178">
+      <c r="G37" s="6">
         <f>IF(D37="+", 1,0)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="180"/>
-      <c r="I37" s="183"/>
-      <c r="J37" s="26" t="str">
+      <c r="H37" s="143"/>
+      <c r="I37" s="125"/>
+      <c r="J37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="176"/>
-      <c r="B38" s="148"/>
-      <c r="C38" s="22" t="s">
+      <c r="A38" s="168"/>
+      <c r="B38" s="170"/>
+      <c r="C38" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="178">
+      <c r="G38" s="6">
         <f>IF(D38="+", 2,0)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="180"/>
-      <c r="I38" s="183"/>
-      <c r="J38" s="26" t="str">
+      <c r="H38" s="143"/>
+      <c r="I38" s="125"/>
+      <c r="J38" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="176"/>
-      <c r="B39" s="148"/>
-      <c r="C39" s="22" t="s">
+      <c r="A39" s="168"/>
+      <c r="B39" s="170"/>
+      <c r="C39" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="24"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="178">
+      <c r="G39" s="6">
         <f>IF(D39="+", 3,0)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="180"/>
-      <c r="I39" s="183"/>
-      <c r="J39" s="26" t="str">
+      <c r="H39" s="143"/>
+      <c r="I39" s="125"/>
+      <c r="J39" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="176"/>
-      <c r="B40" s="149"/>
-      <c r="C40" s="172" t="s">
+      <c r="A40" s="168"/>
+      <c r="B40" s="172"/>
+      <c r="C40" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="173"/>
-      <c r="E40" s="158"/>
-      <c r="F40" s="174"/>
-      <c r="G40" s="179">
+      <c r="D40" s="120"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="123">
         <f>IF(D40="+", 4,0)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="184"/>
-      <c r="I40" s="185"/>
-      <c r="J40" s="26" t="str">
+      <c r="H40" s="176"/>
+      <c r="I40" s="126"/>
+      <c r="J40" s="21" t="str">
         <f t="shared" si="0"/>
         <v>+</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H41" s="187">
+      <c r="H41" s="10">
         <f>IF(AVERAGE(H31:H40)&lt;=0.8,0,IF(AVERAGE(H31:H40)&lt;=1.6,1,IF(AVERAGE(H31:H40)&lt;=2.4,2,IF(AVERAGE(H31:H40)&lt;=3.2,3,IF(AVERAGE(H31:H40)&lt;=4,4)))))</f>
         <v>0</v>
       </c>
@@ -9185,37 +9208,31 @@
         <f>IF(H41=0,"не реализуется",IF(H41=1,"низкий",IF(H41=2,"средний",IF(H41=3,"выше среднего",IF(H41=4,"высокий")))))</f>
         <v>не реализуется</v>
       </c>
-      <c r="K41" t="str">
+      <c r="K41" s="2" t="str">
         <f>IF(H41&lt;4,"+","в рекомендациях не нуждается")</f>
         <v>+</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B43" s="16"/>
+      <c r="A43" s="197"/>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B44" s="17"/>
+      <c r="A44" s="204"/>
+      <c r="B44" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B45" s="7"/>
+      <c r="A45" s="7"/>
+      <c r="B45" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:A40"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="H32:H35"/>
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="H18:H22"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="H28:H30"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="H2:H5"/>
@@ -9223,28 +9240,28 @@
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="B9:B13"/>
     <mergeCell ref="H9:H13"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="H18:H22"/>
+    <mergeCell ref="A31:A40"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="H32:H35"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="H36:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:G40">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J1048576">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1">
+  <conditionalFormatting sqref="K1:K1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"+"</formula>
     </cfRule>
